--- a/research/traditional_assets/database/data/saudi_arabia/saudi_arabia_chemical_specialty.xlsx
+++ b/research/traditional_assets/database/data/saudi_arabia/saudi_arabia_chemical_specialty.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09378112233256991</v>
+        <v>0.09362956008790475</v>
       </c>
       <c r="C2">
-        <v>14115.00846051806</v>
+        <v>14015.722479961</v>
       </c>
       <c r="D2">
-        <v>13239.40846051806</v>
+        <v>13281.361479961</v>
       </c>
       <c r="E2">
-        <v>-49.4</v>
+        <v>91.839</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>141.239</v>
       </c>
       <c r="G2">
         <v>875.6</v>
@@ -1457,28 +1457,28 @@
         <v>851.8</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>7.1043217</v>
       </c>
       <c r="N2">
-        <v>851.8</v>
+        <v>844.6956782999999</v>
       </c>
       <c r="O2">
-        <v>170.36</v>
+        <v>168.93913566</v>
       </c>
       <c r="P2">
-        <v>681.4399999999999</v>
+        <v>675.7565426399999</v>
       </c>
       <c r="Q2">
-        <v>924.64</v>
+        <v>918.95654264</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09378112233256991</v>
+        <v>0.09416884857364118</v>
       </c>
       <c r="T2">
-        <v>0.9352413814778209</v>
+        <v>0.942798887590773</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>119.8988497381812</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09362956008790475</v>
+        <v>0.09347799784323961</v>
       </c>
       <c r="C3">
-        <v>14015.722479961</v>
+        <v>13916.70322594804</v>
       </c>
       <c r="D3">
-        <v>13281.361479961</v>
+        <v>13323.58122594804</v>
       </c>
       <c r="E3">
-        <v>91.839</v>
+        <v>233.078</v>
       </c>
       <c r="F3">
-        <v>141.239</v>
+        <v>282.478</v>
       </c>
       <c r="G3">
         <v>875.6</v>
@@ -1539,28 +1539,28 @@
         <v>851.8</v>
       </c>
       <c r="M3">
-        <v>7.1043217</v>
+        <v>14.2086434</v>
       </c>
       <c r="N3">
-        <v>844.6956782999999</v>
+        <v>837.5913565999999</v>
       </c>
       <c r="O3">
-        <v>168.93913566</v>
+        <v>167.51827132</v>
       </c>
       <c r="P3">
-        <v>675.7565426399999</v>
+        <v>670.07308528</v>
       </c>
       <c r="Q3">
-        <v>918.95654264</v>
+        <v>913.27308528</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09416884857364118</v>
+        <v>0.09456448759514247</v>
       </c>
       <c r="T3">
-        <v>0.942798887590773</v>
+        <v>0.9505106285223567</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>119.8988497381812</v>
+        <v>59.94942486909059</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09347799784323961</v>
+        <v>0.09332643559857448</v>
       </c>
       <c r="C4">
-        <v>13916.70322594804</v>
+        <v>13817.95325025946</v>
       </c>
       <c r="D4">
-        <v>13323.58122594804</v>
+        <v>13366.07025025946</v>
       </c>
       <c r="E4">
-        <v>233.078</v>
+        <v>374.317</v>
       </c>
       <c r="F4">
-        <v>282.478</v>
+        <v>423.717</v>
       </c>
       <c r="G4">
         <v>875.6</v>
@@ -1621,28 +1621,28 @@
         <v>851.8</v>
       </c>
       <c r="M4">
-        <v>14.2086434</v>
+        <v>21.3129651</v>
       </c>
       <c r="N4">
-        <v>837.5913565999999</v>
+        <v>830.4870348999999</v>
       </c>
       <c r="O4">
-        <v>167.51827132</v>
+        <v>166.09740698</v>
       </c>
       <c r="P4">
-        <v>670.07308528</v>
+        <v>664.38962792</v>
       </c>
       <c r="Q4">
-        <v>913.27308528</v>
+        <v>907.58962792</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09456448759514247</v>
+        <v>0.09496828412224173</v>
       </c>
       <c r="T4">
-        <v>0.9505106285223567</v>
+        <v>0.958381374421602</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>59.94942486909059</v>
+        <v>39.9662832460604</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09332643559857448</v>
+        <v>0.09317487335390934</v>
       </c>
       <c r="C5">
-        <v>13817.95325025946</v>
+        <v>13719.47513733028</v>
       </c>
       <c r="D5">
-        <v>13366.07025025946</v>
+        <v>13408.83113733028</v>
       </c>
       <c r="E5">
-        <v>374.317</v>
+        <v>515.556</v>
       </c>
       <c r="F5">
-        <v>423.717</v>
+        <v>564.956</v>
       </c>
       <c r="G5">
         <v>875.6</v>
@@ -1703,28 +1703,28 @@
         <v>851.8</v>
       </c>
       <c r="M5">
-        <v>21.3129651</v>
+        <v>28.4172868</v>
       </c>
       <c r="N5">
-        <v>830.4870348999999</v>
+        <v>823.3827131999999</v>
       </c>
       <c r="O5">
-        <v>166.09740698</v>
+        <v>164.67654264</v>
       </c>
       <c r="P5">
-        <v>664.38962792</v>
+        <v>658.7061705599999</v>
       </c>
       <c r="Q5">
-        <v>907.58962792</v>
+        <v>901.90617056</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09496828412224173</v>
+        <v>0.0953804930769889</v>
       </c>
       <c r="T5">
-        <v>0.958381374421602</v>
+        <v>0.9664160941937483</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>39.9662832460604</v>
+        <v>29.9747124345453</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09317487335390934</v>
+        <v>0.09302331110924419</v>
       </c>
       <c r="C6">
-        <v>13719.47513733028</v>
+        <v>13621.27150477431</v>
       </c>
       <c r="D6">
-        <v>13408.83113733028</v>
+        <v>13451.86650477431</v>
       </c>
       <c r="E6">
-        <v>515.556</v>
+        <v>656.7950000000001</v>
       </c>
       <c r="F6">
-        <v>564.956</v>
+        <v>706.1950000000001</v>
       </c>
       <c r="G6">
         <v>875.6</v>
@@ -1785,28 +1785,28 @@
         <v>851.8</v>
       </c>
       <c r="M6">
-        <v>28.4172868</v>
+        <v>35.5216085</v>
       </c>
       <c r="N6">
-        <v>823.3827131999999</v>
+        <v>816.2783915</v>
       </c>
       <c r="O6">
-        <v>164.67654264</v>
+        <v>163.2556783</v>
       </c>
       <c r="P6">
-        <v>658.7061705599999</v>
+        <v>653.0227132</v>
       </c>
       <c r="Q6">
-        <v>901.90617056</v>
+        <v>896.2227132</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.0953804930769889</v>
+        <v>0.09580138011499389</v>
       </c>
       <c r="T6">
-        <v>0.9664160941937483</v>
+        <v>0.9746199659610975</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>29.9747124345453</v>
+        <v>23.97976994763624</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09302331110924419</v>
+        <v>0.09287174886457907</v>
       </c>
       <c r="C7">
-        <v>13621.27150477431</v>
+        <v>13523.34500391821</v>
       </c>
       <c r="D7">
-        <v>13451.86650477431</v>
+        <v>13495.17900391821</v>
       </c>
       <c r="E7">
-        <v>656.7950000000001</v>
+        <v>798.0340000000001</v>
       </c>
       <c r="F7">
-        <v>706.1950000000001</v>
+        <v>847.4340000000001</v>
       </c>
       <c r="G7">
         <v>875.6</v>
@@ -1867,28 +1867,28 @@
         <v>851.8</v>
       </c>
       <c r="M7">
-        <v>35.5216085</v>
+        <v>42.6259302</v>
       </c>
       <c r="N7">
-        <v>816.2783915</v>
+        <v>809.1740698</v>
       </c>
       <c r="O7">
-        <v>163.2556783</v>
+        <v>161.83481396</v>
       </c>
       <c r="P7">
-        <v>653.0227132</v>
+        <v>647.33925584</v>
       </c>
       <c r="Q7">
-        <v>896.2227132</v>
+        <v>890.53925584</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09580138011499389</v>
+        <v>0.09623122219636071</v>
       </c>
       <c r="T7">
-        <v>0.9746199659610975</v>
+        <v>0.982998388191582</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>23.97976994763624</v>
+        <v>19.9831416230302</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09287174886457907</v>
+        <v>0.09272018661991394</v>
       </c>
       <c r="C8">
-        <v>13523.34500391821</v>
+        <v>13425.69832034611</v>
       </c>
       <c r="D8">
-        <v>13495.17900391821</v>
+        <v>13538.77132034612</v>
       </c>
       <c r="E8">
-        <v>798.034</v>
+        <v>939.2729999999999</v>
       </c>
       <c r="F8">
-        <v>847.434</v>
+        <v>988.6729999999999</v>
       </c>
       <c r="G8">
         <v>875.6</v>
@@ -1949,28 +1949,28 @@
         <v>851.8</v>
       </c>
       <c r="M8">
-        <v>42.6259302</v>
+        <v>49.73025189999999</v>
       </c>
       <c r="N8">
-        <v>809.1740698</v>
+        <v>802.0697481</v>
       </c>
       <c r="O8">
-        <v>161.83481396</v>
+        <v>160.41394962</v>
       </c>
       <c r="P8">
-        <v>647.33925584</v>
+        <v>641.6557984799999</v>
       </c>
       <c r="Q8">
-        <v>890.53925584</v>
+        <v>884.85579848</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09623122219636071</v>
+        <v>0.09667030819345585</v>
       </c>
       <c r="T8">
-        <v>0.982998388191582</v>
+        <v>0.9915569915453026</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>19.9831416230302</v>
+        <v>17.12840710545446</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09272018661991392</v>
+        <v>0.09256862437524881</v>
       </c>
       <c r="C9">
-        <v>13425.69832034612</v>
+        <v>13328.33417445462</v>
       </c>
       <c r="D9">
-        <v>13538.77132034612</v>
+        <v>13582.64617445462</v>
       </c>
       <c r="E9">
-        <v>939.2730000000001</v>
+        <v>1080.512</v>
       </c>
       <c r="F9">
-        <v>988.6730000000001</v>
+        <v>1129.912</v>
       </c>
       <c r="G9">
         <v>875.6</v>
@@ -2031,28 +2031,28 @@
         <v>851.8</v>
       </c>
       <c r="M9">
-        <v>49.73025190000001</v>
+        <v>56.8345736</v>
       </c>
       <c r="N9">
-        <v>802.0697481</v>
+        <v>794.9654264</v>
       </c>
       <c r="O9">
-        <v>160.41394962</v>
+        <v>158.99308528</v>
       </c>
       <c r="P9">
-        <v>641.6557984799999</v>
+        <v>635.97234112</v>
       </c>
       <c r="Q9">
-        <v>884.85579848</v>
+        <v>879.1723411200001</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09667030819345585</v>
+        <v>0.09711893953831391</v>
       </c>
       <c r="T9">
-        <v>0.9915569915453026</v>
+        <v>1.000301651493669</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>17.12840710545445</v>
+        <v>14.98735621727265</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09256862437524881</v>
+        <v>0.09241706213058365</v>
       </c>
       <c r="C10">
-        <v>13328.33417445462</v>
+        <v>13231.25532201875</v>
       </c>
       <c r="D10">
-        <v>13582.64617445462</v>
+        <v>13626.80632201875</v>
       </c>
       <c r="E10">
-        <v>1080.512</v>
+        <v>1221.751</v>
       </c>
       <c r="F10">
-        <v>1129.912</v>
+        <v>1271.151</v>
       </c>
       <c r="G10">
         <v>875.6</v>
@@ -2113,28 +2113,28 @@
         <v>851.8</v>
       </c>
       <c r="M10">
-        <v>56.8345736</v>
+        <v>63.93889529999999</v>
       </c>
       <c r="N10">
-        <v>794.9654264</v>
+        <v>787.8611046999999</v>
       </c>
       <c r="O10">
-        <v>158.99308528</v>
+        <v>157.57222094</v>
       </c>
       <c r="P10">
-        <v>635.97234112</v>
+        <v>630.28888376</v>
       </c>
       <c r="Q10">
-        <v>879.1723411200001</v>
+        <v>873.48888376</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09711893953831391</v>
+        <v>0.09757743091272927</v>
       </c>
       <c r="T10">
-        <v>1.000301651493669</v>
+        <v>1.009238501770571</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>14.98735621727265</v>
+        <v>13.32209441535347</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09241706213058365</v>
+        <v>0.09226549988591851</v>
       </c>
       <c r="C11">
-        <v>13231.25532201875</v>
+        <v>13134.46455476893</v>
       </c>
       <c r="D11">
-        <v>13626.80632201875</v>
+        <v>13671.25455476893</v>
       </c>
       <c r="E11">
-        <v>1221.751</v>
+        <v>1362.99</v>
       </c>
       <c r="F11">
-        <v>1271.151</v>
+        <v>1412.39</v>
       </c>
       <c r="G11">
         <v>875.6</v>
@@ -2195,28 +2195,28 @@
         <v>851.8</v>
       </c>
       <c r="M11">
-        <v>63.93889529999999</v>
+        <v>71.04321699999998</v>
       </c>
       <c r="N11">
-        <v>787.8611046999999</v>
+        <v>780.7567829999999</v>
       </c>
       <c r="O11">
-        <v>157.57222094</v>
+        <v>156.1513566</v>
       </c>
       <c r="P11">
-        <v>630.28888376</v>
+        <v>624.6054263999999</v>
       </c>
       <c r="Q11">
-        <v>873.48888376</v>
+        <v>867.8054264</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09757743091272927</v>
+        <v>0.0980461109843539</v>
       </c>
       <c r="T11">
-        <v>1.009238501770571</v>
+        <v>1.018373948720294</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>13.32209441535347</v>
+        <v>11.98988497381812</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09226549988591851</v>
+        <v>0.09211393764125336</v>
       </c>
       <c r="C12">
-        <v>13134.46455476893</v>
+        <v>13037.96470097928</v>
       </c>
       <c r="D12">
-        <v>13671.25455476893</v>
+        <v>13715.99370097928</v>
       </c>
       <c r="E12">
-        <v>1362.99</v>
+        <v>1504.229</v>
       </c>
       <c r="F12">
-        <v>1412.39</v>
+        <v>1553.629</v>
       </c>
       <c r="G12">
         <v>875.6</v>
@@ -2277,28 +2277,28 @@
         <v>851.8</v>
       </c>
       <c r="M12">
-        <v>71.043217</v>
+        <v>78.1475387</v>
       </c>
       <c r="N12">
-        <v>780.7567829999999</v>
+        <v>773.6524612999999</v>
       </c>
       <c r="O12">
-        <v>156.1513566</v>
+        <v>154.73049226</v>
       </c>
       <c r="P12">
-        <v>624.6054263999999</v>
+        <v>618.9219690399999</v>
       </c>
       <c r="Q12">
-        <v>867.8054264</v>
+        <v>862.12196904</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.0980461109843539</v>
+        <v>0.09852532319241951</v>
       </c>
       <c r="T12">
-        <v>1.018373948720294</v>
+        <v>1.027714686612706</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>11.98988497381812</v>
+        <v>10.89989543074374</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09211393764125336</v>
+        <v>0.09196237539658822</v>
       </c>
       <c r="C13">
-        <v>13037.96470097928</v>
+        <v>12941.7586260676</v>
       </c>
       <c r="D13">
-        <v>13715.99370097928</v>
+        <v>13761.0266260676</v>
       </c>
       <c r="E13">
-        <v>1504.229</v>
+        <v>1645.468</v>
       </c>
       <c r="F13">
-        <v>1553.629</v>
+        <v>1694.868</v>
       </c>
       <c r="G13">
         <v>875.6</v>
@@ -2359,28 +2359,28 @@
         <v>851.8</v>
       </c>
       <c r="M13">
-        <v>78.1475387</v>
+        <v>85.2518604</v>
       </c>
       <c r="N13">
-        <v>773.6524612999999</v>
+        <v>766.5481396</v>
       </c>
       <c r="O13">
-        <v>154.73049226</v>
+        <v>153.30962792</v>
       </c>
       <c r="P13">
-        <v>618.9219690399999</v>
+        <v>613.23851168</v>
       </c>
       <c r="Q13">
-        <v>862.12196904</v>
+        <v>856.43851168</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09852532319241951</v>
+        <v>0.09901542658703208</v>
       </c>
       <c r="T13">
-        <v>1.027714686612706</v>
+        <v>1.037267714002674</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>10.89989543074374</v>
+        <v>9.9915708115151</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09196237539658822</v>
+        <v>0.09181081315192308</v>
       </c>
       <c r="C14">
-        <v>12941.7586260676</v>
+        <v>12845.84923320705</v>
       </c>
       <c r="D14">
-        <v>13761.0266260676</v>
+        <v>13806.35623320705</v>
       </c>
       <c r="E14">
-        <v>1645.468</v>
+        <v>1786.707</v>
       </c>
       <c r="F14">
-        <v>1694.868</v>
+        <v>1836.107</v>
       </c>
       <c r="G14">
         <v>875.6</v>
@@ -2441,28 +2441,28 @@
         <v>851.8</v>
       </c>
       <c r="M14">
-        <v>85.2518604</v>
+        <v>92.3561821</v>
       </c>
       <c r="N14">
-        <v>766.5481396</v>
+        <v>759.4438179</v>
       </c>
       <c r="O14">
-        <v>153.30962792</v>
+        <v>151.88876358</v>
       </c>
       <c r="P14">
-        <v>613.23851168</v>
+        <v>607.55505432</v>
       </c>
       <c r="Q14">
-        <v>856.43851168</v>
+        <v>850.75505432</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09901542658703208</v>
+        <v>0.09951679672634836</v>
       </c>
       <c r="T14">
-        <v>1.037267714002674</v>
+        <v>1.047040351217698</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>9.9915708115151</v>
+        <v>9.222988441398554</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09181081315192308</v>
+        <v>0.09182725090725796</v>
       </c>
       <c r="C15">
-        <v>12845.84923320705</v>
+        <v>12699.67955624168</v>
       </c>
       <c r="D15">
-        <v>13806.35623320705</v>
+        <v>13801.42555624168</v>
       </c>
       <c r="E15">
-        <v>1786.707</v>
+        <v>1927.946</v>
       </c>
       <c r="F15">
-        <v>1836.107</v>
+        <v>1977.346</v>
       </c>
       <c r="G15">
         <v>875.6</v>
@@ -2523,45 +2523,45 @@
         <v>851.8</v>
       </c>
       <c r="M15">
-        <v>92.3561821</v>
+        <v>102.4265228</v>
       </c>
       <c r="N15">
-        <v>759.4438179</v>
+        <v>749.3734771999999</v>
       </c>
       <c r="O15">
-        <v>151.88876358</v>
+        <v>149.87469544</v>
       </c>
       <c r="P15">
-        <v>607.55505432</v>
+        <v>599.4987817599999</v>
       </c>
       <c r="Q15">
-        <v>850.75505432</v>
+        <v>842.69878176</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09951679672634836</v>
+        <v>0.1000298266363465</v>
       </c>
       <c r="T15">
-        <v>1.047040351217698</v>
+        <v>1.05704025906563</v>
       </c>
       <c r="U15">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V15">
         <v>0.2</v>
       </c>
       <c r="W15">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y15">
-        <v>9.222988441398554</v>
+        <v>8.316205380350954</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09182725090725796</v>
+        <v>0.09168768866259279</v>
       </c>
       <c r="C16">
-        <v>12699.67955624168</v>
+        <v>12600.41604000098</v>
       </c>
       <c r="D16">
-        <v>13801.42555624168</v>
+        <v>13843.40104000098</v>
       </c>
       <c r="E16">
-        <v>1927.946</v>
+        <v>2069.185</v>
       </c>
       <c r="F16">
-        <v>1977.346</v>
+        <v>2118.585</v>
       </c>
       <c r="G16">
         <v>875.6</v>
@@ -2605,28 +2605,28 @@
         <v>851.8</v>
       </c>
       <c r="M16">
-        <v>102.4265228</v>
+        <v>109.742703</v>
       </c>
       <c r="N16">
-        <v>749.3734771999999</v>
+        <v>742.0572969999999</v>
       </c>
       <c r="O16">
-        <v>149.87469544</v>
+        <v>148.4114594</v>
       </c>
       <c r="P16">
-        <v>599.4987817599999</v>
+        <v>593.6458375999999</v>
       </c>
       <c r="Q16">
-        <v>842.69878176</v>
+        <v>836.8458376</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1000298266363465</v>
+        <v>0.1005549278383445</v>
       </c>
       <c r="T16">
-        <v>1.05704025906563</v>
+        <v>1.067275458862925</v>
       </c>
       <c r="U16">
         <v>0.0518</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>8.316205380350954</v>
+        <v>7.761791688327559</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09168768866259279</v>
+        <v>0.09154812641792766</v>
       </c>
       <c r="C17">
-        <v>12600.41604000098</v>
+        <v>12501.40863010573</v>
       </c>
       <c r="D17">
-        <v>13843.40104000098</v>
+        <v>13885.63263010573</v>
       </c>
       <c r="E17">
-        <v>2069.185</v>
+        <v>2210.424</v>
       </c>
       <c r="F17">
-        <v>2118.585</v>
+        <v>2259.824</v>
       </c>
       <c r="G17">
         <v>875.6</v>
@@ -2687,28 +2687,28 @@
         <v>851.8</v>
       </c>
       <c r="M17">
-        <v>109.742703</v>
+        <v>117.0588832</v>
       </c>
       <c r="N17">
-        <v>742.0572969999999</v>
+        <v>734.7411168</v>
       </c>
       <c r="O17">
-        <v>148.4114594</v>
+        <v>146.94822336</v>
       </c>
       <c r="P17">
-        <v>593.6458375999999</v>
+        <v>587.7928934399999</v>
       </c>
       <c r="Q17">
-        <v>836.8458376</v>
+        <v>830.99289344</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1005549278383445</v>
+        <v>0.1010925314499139</v>
       </c>
       <c r="T17">
-        <v>1.067275458862925</v>
+        <v>1.077754353893489</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>7.761791688327559</v>
+        <v>7.276679707807087</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09154812641792766</v>
+        <v>0.09140856417326251</v>
       </c>
       <c r="C18">
-        <v>12501.40863010573</v>
+        <v>12402.65967761284</v>
       </c>
       <c r="D18">
-        <v>13885.63263010573</v>
+        <v>13928.12267761284</v>
       </c>
       <c r="E18">
-        <v>2210.424</v>
+        <v>2351.663</v>
       </c>
       <c r="F18">
-        <v>2259.824</v>
+        <v>2401.063</v>
       </c>
       <c r="G18">
         <v>875.6</v>
@@ -2769,28 +2769,28 @@
         <v>851.8</v>
       </c>
       <c r="M18">
-        <v>117.0588832</v>
+        <v>124.3750634</v>
       </c>
       <c r="N18">
-        <v>734.7411168</v>
+        <v>727.4249365999999</v>
       </c>
       <c r="O18">
-        <v>146.94822336</v>
+        <v>145.48498732</v>
       </c>
       <c r="P18">
-        <v>587.7928934399999</v>
+        <v>581.93994928</v>
       </c>
       <c r="Q18">
-        <v>830.99289344</v>
+        <v>825.13994928</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1010925314499139</v>
+        <v>0.1016430893653765</v>
       </c>
       <c r="T18">
-        <v>1.077754353893489</v>
+        <v>1.088485752418765</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>7.276679707807087</v>
+        <v>6.848639724994905</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09140856417326251</v>
+        <v>0.09151380192859739</v>
       </c>
       <c r="C19">
-        <v>12402.65967761284</v>
+        <v>12229.35674276643</v>
       </c>
       <c r="D19">
-        <v>13928.12267761284</v>
+        <v>13896.05874276642</v>
       </c>
       <c r="E19">
-        <v>2351.663</v>
+        <v>2492.902</v>
       </c>
       <c r="F19">
-        <v>2401.063</v>
+        <v>2542.302</v>
       </c>
       <c r="G19">
         <v>875.6</v>
@@ -2851,45 +2851,45 @@
         <v>851.8</v>
       </c>
       <c r="M19">
-        <v>124.3750634</v>
+        <v>136.013157</v>
       </c>
       <c r="N19">
-        <v>727.4249365999999</v>
+        <v>715.786843</v>
       </c>
       <c r="O19">
-        <v>145.48498732</v>
+        <v>143.1573686</v>
       </c>
       <c r="P19">
-        <v>581.93994928</v>
+        <v>572.6294743999999</v>
       </c>
       <c r="Q19">
-        <v>825.13994928</v>
+        <v>815.8294744</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1016430893653765</v>
+        <v>0.1022070755226797</v>
       </c>
       <c r="T19">
-        <v>1.088485752418765</v>
+        <v>1.099478892371487</v>
       </c>
       <c r="U19">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V19">
         <v>0.2</v>
       </c>
       <c r="W19">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y19">
-        <v>6.848639724994905</v>
+        <v>6.262629430768966</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.0915138019285974</v>
+        <v>0.09138783968393226</v>
       </c>
       <c r="C20">
-        <v>12229.35674276642</v>
+        <v>12126.51348082668</v>
       </c>
       <c r="D20">
-        <v>13896.05874276642</v>
+        <v>13934.45448082668</v>
       </c>
       <c r="E20">
-        <v>2492.902</v>
+        <v>2634.141</v>
       </c>
       <c r="F20">
-        <v>2542.302</v>
+        <v>2683.541</v>
       </c>
       <c r="G20">
         <v>875.6</v>
@@ -2933,28 +2933,28 @@
         <v>851.8</v>
       </c>
       <c r="M20">
-        <v>136.013157</v>
+        <v>143.5694435</v>
       </c>
       <c r="N20">
-        <v>715.786843</v>
+        <v>708.2305564999999</v>
       </c>
       <c r="O20">
-        <v>143.1573686</v>
+        <v>141.6461113</v>
       </c>
       <c r="P20">
-        <v>572.6294743999999</v>
+        <v>566.5844451999999</v>
       </c>
       <c r="Q20">
-        <v>815.8294744</v>
+        <v>809.7844451999999</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1022070755226797</v>
+        <v>0.1027849872641139</v>
       </c>
       <c r="T20">
-        <v>1.099478892371487</v>
+        <v>1.110743467878597</v>
       </c>
       <c r="U20">
         <v>0.0535</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>6.262629430768967</v>
+        <v>5.933017355465336</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09138783968393226</v>
+        <v>0.0912618774392671</v>
       </c>
       <c r="C21">
-        <v>12126.51348082668</v>
+        <v>12023.88298675419</v>
       </c>
       <c r="D21">
-        <v>13934.45448082668</v>
+        <v>13973.06298675419</v>
       </c>
       <c r="E21">
-        <v>2634.141</v>
+        <v>2775.38</v>
       </c>
       <c r="F21">
-        <v>2683.541</v>
+        <v>2824.78</v>
       </c>
       <c r="G21">
         <v>875.6</v>
@@ -3015,28 +3015,28 @@
         <v>851.8</v>
       </c>
       <c r="M21">
-        <v>143.5694435</v>
+        <v>151.12573</v>
       </c>
       <c r="N21">
-        <v>708.2305564999999</v>
+        <v>700.67427</v>
       </c>
       <c r="O21">
-        <v>141.6461113</v>
+        <v>140.134854</v>
       </c>
       <c r="P21">
-        <v>566.5844451999999</v>
+        <v>560.539416</v>
       </c>
       <c r="Q21">
-        <v>809.7844451999999</v>
+        <v>803.739416</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1027849872641139</v>
+        <v>0.1033773467990839</v>
       </c>
       <c r="T21">
-        <v>1.110743467878597</v>
+        <v>1.122289657773385</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.933017355465336</v>
+        <v>5.636366487692069</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.0912618774392671</v>
+        <v>0.09127031519460196</v>
       </c>
       <c r="C22">
-        <v>12023.88298675419</v>
+        <v>11880.05105802131</v>
       </c>
       <c r="D22">
-        <v>13973.06298675419</v>
+        <v>13970.47005802131</v>
       </c>
       <c r="E22">
-        <v>2775.38</v>
+        <v>2916.619</v>
       </c>
       <c r="F22">
-        <v>2824.78</v>
+        <v>2966.019</v>
       </c>
       <c r="G22">
         <v>875.6</v>
@@ -3097,45 +3097,45 @@
         <v>851.8</v>
       </c>
       <c r="M22">
-        <v>151.12573</v>
+        <v>161.0548317</v>
       </c>
       <c r="N22">
-        <v>700.67427</v>
+        <v>690.7451682999999</v>
       </c>
       <c r="O22">
-        <v>140.134854</v>
+        <v>138.14903366</v>
       </c>
       <c r="P22">
-        <v>560.539416</v>
+        <v>552.5961346399999</v>
       </c>
       <c r="Q22">
-        <v>803.739416</v>
+        <v>795.79613464</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1033773467990839</v>
+        <v>0.1039847027779772</v>
       </c>
       <c r="T22">
-        <v>1.122289657773385</v>
+        <v>1.134128156273104</v>
       </c>
       <c r="U22">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V22">
         <v>0.2</v>
       </c>
       <c r="W22">
-        <v>0.0428</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y22">
-        <v>5.636366487692069</v>
+        <v>5.288881997571265</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09127031519460196</v>
+        <v>0.09115075294993684</v>
       </c>
       <c r="C23">
-        <v>11880.05105802131</v>
+        <v>11775.64365728953</v>
       </c>
       <c r="D23">
-        <v>13970.47005802131</v>
+        <v>14007.30165728953</v>
       </c>
       <c r="E23">
-        <v>2916.619</v>
+        <v>3057.858</v>
       </c>
       <c r="F23">
-        <v>2966.019</v>
+        <v>3107.258</v>
       </c>
       <c r="G23">
         <v>875.6</v>
@@ -3179,28 +3179,28 @@
         <v>851.8</v>
       </c>
       <c r="M23">
-        <v>161.0548317</v>
+        <v>168.7241094</v>
       </c>
       <c r="N23">
-        <v>690.7451682999999</v>
+        <v>683.0758906</v>
       </c>
       <c r="O23">
-        <v>138.14903366</v>
+        <v>136.61517812</v>
       </c>
       <c r="P23">
-        <v>552.5961346399999</v>
+        <v>546.46071248</v>
       </c>
       <c r="Q23">
-        <v>795.79613464</v>
+        <v>789.66071248</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1039847027779772</v>
+        <v>0.1046076319870985</v>
       </c>
       <c r="T23">
-        <v>1.134128156273104</v>
+        <v>1.146270206016406</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.288881997571266</v>
+        <v>5.048478270408935</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09115075294993684</v>
+        <v>0.0910311907052717</v>
       </c>
       <c r="C24">
-        <v>11775.64365728953</v>
+        <v>11671.43097478712</v>
       </c>
       <c r="D24">
-        <v>14007.30165728953</v>
+        <v>14044.32797478711</v>
       </c>
       <c r="E24">
-        <v>3057.858</v>
+        <v>3199.097</v>
       </c>
       <c r="F24">
-        <v>3107.258</v>
+        <v>3248.497</v>
       </c>
       <c r="G24">
         <v>875.6</v>
@@ -3261,28 +3261,28 @@
         <v>851.8</v>
       </c>
       <c r="M24">
-        <v>168.7241094</v>
+        <v>176.3933871</v>
       </c>
       <c r="N24">
-        <v>683.0758906</v>
+        <v>675.4066129</v>
       </c>
       <c r="O24">
-        <v>136.61517812</v>
+        <v>135.08132258</v>
       </c>
       <c r="P24">
-        <v>546.46071248</v>
+        <v>540.32529032</v>
       </c>
       <c r="Q24">
-        <v>789.66071248</v>
+        <v>783.5252903200001</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1046076319870985</v>
+        <v>0.1052467411756775</v>
       </c>
       <c r="T24">
-        <v>1.146270206016406</v>
+        <v>1.158727633675118</v>
       </c>
       <c r="U24">
         <v>0.0543</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.048478270408935</v>
+        <v>4.828979215173765</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.0910311907052717</v>
+        <v>0.09091162846060656</v>
       </c>
       <c r="C25">
-        <v>11671.43097478712</v>
+        <v>11567.41455873673</v>
       </c>
       <c r="D25">
-        <v>14044.32797478711</v>
+        <v>14081.55055873673</v>
       </c>
       <c r="E25">
-        <v>3199.097</v>
+        <v>3340.336</v>
       </c>
       <c r="F25">
-        <v>3248.497</v>
+        <v>3389.736</v>
       </c>
       <c r="G25">
         <v>875.6</v>
@@ -3343,28 +3343,28 @@
         <v>851.8</v>
       </c>
       <c r="M25">
-        <v>176.3933871</v>
+        <v>184.0626648</v>
       </c>
       <c r="N25">
-        <v>675.4066129</v>
+        <v>667.7373352</v>
       </c>
       <c r="O25">
-        <v>135.08132258</v>
+        <v>133.54746704</v>
       </c>
       <c r="P25">
-        <v>540.32529032</v>
+        <v>534.1898681599999</v>
       </c>
       <c r="Q25">
-        <v>783.5252903200001</v>
+        <v>777.38986816</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1052467411756775</v>
+        <v>0.1059026690271139</v>
       </c>
       <c r="T25">
-        <v>1.158727633675118</v>
+        <v>1.171512888377481</v>
       </c>
       <c r="U25">
         <v>0.0543</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>4.828979215173765</v>
+        <v>4.627771747874856</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09091162846060655</v>
+        <v>0.09079206621594141</v>
       </c>
       <c r="C26">
-        <v>11567.41455873674</v>
+        <v>11463.59597381809</v>
       </c>
       <c r="D26">
-        <v>14081.55055873674</v>
+        <v>14118.97097381809</v>
       </c>
       <c r="E26">
-        <v>3340.336</v>
+        <v>3481.575</v>
       </c>
       <c r="F26">
-        <v>3389.736</v>
+        <v>3530.975</v>
       </c>
       <c r="G26">
         <v>875.6</v>
@@ -3425,28 +3425,28 @@
         <v>851.8</v>
       </c>
       <c r="M26">
-        <v>184.0626648</v>
+        <v>191.7319425</v>
       </c>
       <c r="N26">
-        <v>667.7373352</v>
+        <v>660.0680574999999</v>
       </c>
       <c r="O26">
-        <v>133.54746704</v>
+        <v>132.0136115</v>
       </c>
       <c r="P26">
-        <v>534.1898681599999</v>
+        <v>528.0544459999999</v>
       </c>
       <c r="Q26">
-        <v>777.38986816</v>
+        <v>771.2544459999999</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1059026690271139</v>
+        <v>0.1065760882879219</v>
       </c>
       <c r="T26">
-        <v>1.171512888377481</v>
+        <v>1.18463908320524</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>4.627771747874857</v>
+        <v>4.442660877959863</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09079206621594141</v>
+        <v>0.09067250397127627</v>
       </c>
       <c r="C27">
-        <v>11463.59597381809</v>
+        <v>11359.97680138716</v>
       </c>
       <c r="D27">
-        <v>14118.97097381809</v>
+        <v>14156.59080138716</v>
       </c>
       <c r="E27">
-        <v>3481.575</v>
+        <v>3622.814</v>
       </c>
       <c r="F27">
-        <v>3530.975</v>
+        <v>3672.214</v>
       </c>
       <c r="G27">
         <v>875.6</v>
@@ -3507,28 +3507,28 @@
         <v>851.8</v>
       </c>
       <c r="M27">
-        <v>191.7319425</v>
+        <v>199.4012202</v>
       </c>
       <c r="N27">
-        <v>660.0680574999999</v>
+        <v>652.3987797999999</v>
       </c>
       <c r="O27">
-        <v>132.0136115</v>
+        <v>130.47975596</v>
       </c>
       <c r="P27">
-        <v>528.0544459999999</v>
+        <v>521.9190238399999</v>
       </c>
       <c r="Q27">
-        <v>771.2544459999999</v>
+        <v>765.11902384</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1065760882879219</v>
+        <v>0.1072677080692923</v>
       </c>
       <c r="T27">
-        <v>1.18463908320524</v>
+        <v>1.198120040055371</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>4.442660877959863</v>
+        <v>4.271789305730637</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09067250397127627</v>
+        <v>0.09076894172661112</v>
       </c>
       <c r="C28">
-        <v>11359.97680138716</v>
+        <v>11188.37840693265</v>
       </c>
       <c r="D28">
-        <v>14156.59080138716</v>
+        <v>14126.23140693265</v>
       </c>
       <c r="E28">
-        <v>3622.814</v>
+        <v>3764.053</v>
       </c>
       <c r="F28">
-        <v>3672.214</v>
+        <v>3813.453</v>
       </c>
       <c r="G28">
         <v>875.6</v>
@@ -3589,45 +3589,45 @@
         <v>851.8</v>
       </c>
       <c r="M28">
-        <v>199.4012202</v>
+        <v>210.8839509</v>
       </c>
       <c r="N28">
-        <v>652.3987797999999</v>
+        <v>640.9160491</v>
       </c>
       <c r="O28">
-        <v>130.47975596</v>
+        <v>128.18320982</v>
       </c>
       <c r="P28">
-        <v>521.9190238399999</v>
+        <v>512.73283928</v>
       </c>
       <c r="Q28">
-        <v>765.11902384</v>
+        <v>755.9328392800001</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1072677080692923</v>
+        <v>0.1079782763378235</v>
       </c>
       <c r="T28">
-        <v>1.198120040055371</v>
+        <v>1.211970338189067</v>
       </c>
       <c r="U28">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V28">
         <v>0.2</v>
       </c>
       <c r="W28">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y28">
-        <v>4.271789305730637</v>
+        <v>4.039188361014342</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09076894172661112</v>
+        <v>0.09065737948194599</v>
       </c>
       <c r="C29">
-        <v>11188.37840693265</v>
+        <v>11082.27195597178</v>
       </c>
       <c r="D29">
-        <v>14126.23140693265</v>
+        <v>14161.36395597178</v>
       </c>
       <c r="E29">
-        <v>3764.053</v>
+        <v>3905.292</v>
       </c>
       <c r="F29">
-        <v>3813.453</v>
+        <v>3954.692</v>
       </c>
       <c r="G29">
         <v>875.6</v>
@@ -3671,28 +3671,28 @@
         <v>851.8</v>
       </c>
       <c r="M29">
-        <v>210.8839509</v>
+        <v>218.6944676</v>
       </c>
       <c r="N29">
-        <v>640.9160491</v>
+        <v>633.1055323999999</v>
       </c>
       <c r="O29">
-        <v>128.18320982</v>
+        <v>126.62110648</v>
       </c>
       <c r="P29">
-        <v>512.73283928</v>
+        <v>506.4844259199999</v>
       </c>
       <c r="Q29">
-        <v>755.9328392800001</v>
+        <v>749.68442592</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1079782763378235</v>
+        <v>0.1087085826138139</v>
       </c>
       <c r="T29">
-        <v>1.211970338189067</v>
+        <v>1.226205366826476</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.039188361014342</v>
+        <v>3.894931633835258</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09065737948194599</v>
+        <v>0.09054581723728083</v>
       </c>
       <c r="C30">
-        <v>11082.27195597178</v>
+        <v>10976.34069305189</v>
       </c>
       <c r="D30">
-        <v>14161.36395597178</v>
+        <v>14196.67169305189</v>
       </c>
       <c r="E30">
-        <v>3905.292</v>
+        <v>4046.531</v>
       </c>
       <c r="F30">
-        <v>3954.692</v>
+        <v>4095.931</v>
       </c>
       <c r="G30">
         <v>875.6</v>
@@ -3753,28 +3753,28 @@
         <v>851.8</v>
       </c>
       <c r="M30">
-        <v>218.6944676</v>
+        <v>226.5049843</v>
       </c>
       <c r="N30">
-        <v>633.1055323999999</v>
+        <v>625.2950156999999</v>
       </c>
       <c r="O30">
-        <v>126.62110648</v>
+        <v>125.05900314</v>
       </c>
       <c r="P30">
-        <v>506.4844259199999</v>
+        <v>500.2360125599999</v>
       </c>
       <c r="Q30">
-        <v>749.68442592</v>
+        <v>743.43601256</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1087085826138139</v>
+        <v>0.1094594608975787</v>
       </c>
       <c r="T30">
-        <v>1.226205366826476</v>
+        <v>1.240841382186067</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>3.894931633835258</v>
+        <v>3.760623646461628</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09054581723728083</v>
+        <v>0.09043425499261572</v>
       </c>
       <c r="C31">
-        <v>10976.34069305189</v>
+        <v>10870.58593180781</v>
       </c>
       <c r="D31">
-        <v>14196.67169305189</v>
+        <v>14232.15593180781</v>
       </c>
       <c r="E31">
-        <v>4046.530999999999</v>
+        <v>4187.77</v>
       </c>
       <c r="F31">
-        <v>4095.931</v>
+        <v>4237.17</v>
       </c>
       <c r="G31">
         <v>875.6</v>
@@ -3835,28 +3835,28 @@
         <v>851.8</v>
       </c>
       <c r="M31">
-        <v>226.5049843</v>
+        <v>234.315501</v>
       </c>
       <c r="N31">
-        <v>625.2950157</v>
+        <v>617.4844989999999</v>
       </c>
       <c r="O31">
-        <v>125.05900314</v>
+        <v>123.4968998</v>
       </c>
       <c r="P31">
-        <v>500.23601256</v>
+        <v>493.9875991999999</v>
       </c>
       <c r="Q31">
-        <v>743.4360125600001</v>
+        <v>737.1875992</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1094594608975787</v>
+        <v>0.1102317928465939</v>
       </c>
       <c r="T31">
-        <v>1.240841382186067</v>
+        <v>1.255895569413074</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.760623646461629</v>
+        <v>3.635269524912907</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09043425499261572</v>
+        <v>0.09032269274795057</v>
       </c>
       <c r="C32">
-        <v>10870.58593180781</v>
+        <v>10765.00899904093</v>
       </c>
       <c r="D32">
-        <v>14232.15593180781</v>
+        <v>14267.81799904093</v>
       </c>
       <c r="E32">
-        <v>4187.77</v>
+        <v>4329.009</v>
       </c>
       <c r="F32">
-        <v>4237.17</v>
+        <v>4378.409</v>
       </c>
       <c r="G32">
         <v>875.6</v>
@@ -3917,28 +3917,28 @@
         <v>851.8</v>
       </c>
       <c r="M32">
-        <v>234.315501</v>
+        <v>242.1260177</v>
       </c>
       <c r="N32">
-        <v>617.4844989999999</v>
+        <v>609.6739823</v>
       </c>
       <c r="O32">
-        <v>123.4968998</v>
+        <v>121.93479646</v>
       </c>
       <c r="P32">
-        <v>493.9875991999999</v>
+        <v>487.73918584</v>
       </c>
       <c r="Q32">
-        <v>737.1875992</v>
+        <v>730.9391858400001</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1102317928465939</v>
+        <v>0.1110265112289139</v>
       </c>
       <c r="T32">
-        <v>1.255895569413074</v>
+        <v>1.271386109893038</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.635269524912907</v>
+        <v>3.51800276604475</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09032269274795057</v>
+        <v>0.09021113050328543</v>
       </c>
       <c r="C33">
-        <v>10765.00899904093</v>
+        <v>10659.61123488448</v>
       </c>
       <c r="D33">
-        <v>14267.81799904093</v>
+        <v>14303.65923488448</v>
       </c>
       <c r="E33">
-        <v>4329.009</v>
+        <v>4470.248000000001</v>
       </c>
       <c r="F33">
-        <v>4378.409</v>
+        <v>4519.648</v>
       </c>
       <c r="G33">
         <v>875.6</v>
@@ -3999,28 +3999,28 @@
         <v>851.8</v>
       </c>
       <c r="M33">
-        <v>242.1260177</v>
+        <v>249.9365344</v>
       </c>
       <c r="N33">
-        <v>609.6739823</v>
+        <v>601.8634655999999</v>
       </c>
       <c r="O33">
-        <v>121.93479646</v>
+        <v>120.37269312</v>
       </c>
       <c r="P33">
-        <v>487.73918584</v>
+        <v>481.4907724799999</v>
       </c>
       <c r="Q33">
-        <v>730.9391858400001</v>
+        <v>724.69077248</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1110265112289139</v>
+        <v>0.1118446036813021</v>
       </c>
       <c r="T33">
-        <v>1.271386109893038</v>
+        <v>1.287332254504765</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.51800276604475</v>
+        <v>3.408065179605851</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09021113050328543</v>
+        <v>0.0900995682586203</v>
       </c>
       <c r="C34">
-        <v>10659.61123488448</v>
+        <v>10554.39399297144</v>
       </c>
       <c r="D34">
-        <v>14303.65923488448</v>
+        <v>14339.68099297144</v>
       </c>
       <c r="E34">
-        <v>4470.248000000001</v>
+        <v>4611.487</v>
       </c>
       <c r="F34">
-        <v>4519.648</v>
+        <v>4660.887</v>
       </c>
       <c r="G34">
         <v>875.6</v>
@@ -4081,28 +4081,28 @@
         <v>851.8</v>
       </c>
       <c r="M34">
-        <v>249.9365344</v>
+        <v>257.7470511</v>
       </c>
       <c r="N34">
-        <v>601.8634655999999</v>
+        <v>594.0529488999999</v>
       </c>
       <c r="O34">
-        <v>120.37269312</v>
+        <v>118.81058978</v>
       </c>
       <c r="P34">
-        <v>481.4907724799999</v>
+        <v>475.2423591199999</v>
       </c>
       <c r="Q34">
-        <v>724.69077248</v>
+        <v>718.44235912</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1118446036813021</v>
+        <v>0.1126871168039109</v>
       </c>
       <c r="T34">
-        <v>1.287332254504765</v>
+        <v>1.303754403433261</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.408065179605851</v>
+        <v>3.304790477193552</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.0900995682586203</v>
+        <v>0.08998800601395515</v>
       </c>
       <c r="C35">
-        <v>10554.39399297144</v>
+        <v>10449.35864060498</v>
       </c>
       <c r="D35">
-        <v>14339.68099297144</v>
+        <v>14375.88464060498</v>
       </c>
       <c r="E35">
-        <v>4611.487</v>
+        <v>4752.726000000001</v>
       </c>
       <c r="F35">
-        <v>4660.887</v>
+        <v>4802.126</v>
       </c>
       <c r="G35">
         <v>875.6</v>
@@ -4163,28 +4163,28 @@
         <v>851.8</v>
       </c>
       <c r="M35">
-        <v>257.7470511</v>
+        <v>265.5575678</v>
       </c>
       <c r="N35">
-        <v>594.0529488999999</v>
+        <v>586.2424321999999</v>
       </c>
       <c r="O35">
-        <v>118.81058978</v>
+        <v>117.24848644</v>
       </c>
       <c r="P35">
-        <v>475.2423591199999</v>
+        <v>468.99394576</v>
       </c>
       <c r="Q35">
-        <v>718.44235912</v>
+        <v>712.19394576</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1126871168039109</v>
+        <v>0.1135551606272048</v>
       </c>
       <c r="T35">
-        <v>1.303754403433261</v>
+        <v>1.320674193238377</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.304790477193552</v>
+        <v>3.207590757276095</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08998800601395515</v>
+        <v>0.08987644376929001</v>
       </c>
       <c r="C36">
-        <v>10449.35864060498</v>
+        <v>10344.50655893142</v>
       </c>
       <c r="D36">
-        <v>14375.88464060498</v>
+        <v>14412.27155893142</v>
       </c>
       <c r="E36">
-        <v>4752.726000000001</v>
+        <v>4893.965000000001</v>
       </c>
       <c r="F36">
-        <v>4802.126</v>
+        <v>4943.365000000001</v>
       </c>
       <c r="G36">
         <v>875.6</v>
@@ -4245,28 +4245,28 @@
         <v>851.8</v>
       </c>
       <c r="M36">
-        <v>265.5575678</v>
+        <v>273.3680845000001</v>
       </c>
       <c r="N36">
-        <v>586.2424321999999</v>
+        <v>578.4319154999998</v>
       </c>
       <c r="O36">
-        <v>117.24848644</v>
+        <v>115.6863831</v>
       </c>
       <c r="P36">
-        <v>468.99394576</v>
+        <v>462.7455323999999</v>
       </c>
       <c r="Q36">
-        <v>712.19394576</v>
+        <v>705.9455323999999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1135551606272048</v>
+        <v>0.1144499134912154</v>
       </c>
       <c r="T36">
-        <v>1.320674193238377</v>
+        <v>1.338114591960575</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.207590757276095</v>
+        <v>3.115945307068205</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08987644376929001</v>
+        <v>0.08976488152462488</v>
       </c>
       <c r="C37">
-        <v>10344.50655893142</v>
+        <v>10239.83914311588</v>
       </c>
       <c r="D37">
-        <v>14412.27155893142</v>
+        <v>14448.84314311588</v>
       </c>
       <c r="E37">
-        <v>4893.965000000001</v>
+        <v>5035.204000000001</v>
       </c>
       <c r="F37">
-        <v>4943.365000000001</v>
+        <v>5084.604</v>
       </c>
       <c r="G37">
         <v>875.6</v>
@@ -4327,28 +4327,28 @@
         <v>851.8</v>
       </c>
       <c r="M37">
-        <v>273.3680845000001</v>
+        <v>281.1786012</v>
       </c>
       <c r="N37">
-        <v>578.4319154999998</v>
+        <v>570.6213988</v>
       </c>
       <c r="O37">
-        <v>115.6863831</v>
+        <v>114.12427976</v>
       </c>
       <c r="P37">
-        <v>462.7455323999999</v>
+        <v>456.49711904</v>
       </c>
       <c r="Q37">
-        <v>705.9455323999999</v>
+        <v>699.69711904</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1144499134912154</v>
+        <v>0.1153726273822264</v>
       </c>
       <c r="T37">
-        <v>1.338114591960575</v>
+        <v>1.356100003142841</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.115945307068205</v>
+        <v>3.029391270760756</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08976488152462489</v>
+        <v>0.09039331927995972</v>
       </c>
       <c r="C38">
-        <v>10239.83914311588</v>
+        <v>9894.977746338489</v>
       </c>
       <c r="D38">
-        <v>14448.84314311588</v>
+        <v>14245.22074633849</v>
       </c>
       <c r="E38">
-        <v>5035.204</v>
+        <v>5176.443</v>
       </c>
       <c r="F38">
-        <v>5084.603999999999</v>
+        <v>5225.843</v>
       </c>
       <c r="G38">
         <v>875.6</v>
@@ -4409,45 +4409,45 @@
         <v>851.8</v>
       </c>
       <c r="M38">
-        <v>281.1786012</v>
+        <v>302.0537254</v>
       </c>
       <c r="N38">
-        <v>570.6213988</v>
+        <v>549.7462745999999</v>
       </c>
       <c r="O38">
-        <v>114.12427976</v>
+        <v>109.94925492</v>
       </c>
       <c r="P38">
-        <v>456.49711904</v>
+        <v>439.7970196799999</v>
       </c>
       <c r="Q38">
-        <v>699.69711904</v>
+        <v>682.99701968</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1153726273822264</v>
+        <v>0.1163246337777138</v>
       </c>
       <c r="T38">
-        <v>1.35610000314284</v>
+        <v>1.374656379759464</v>
       </c>
       <c r="U38">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V38">
         <v>0.2</v>
       </c>
       <c r="W38">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y38">
-        <v>3.029391270760756</v>
+        <v>2.820028122056725</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09039331927995972</v>
+        <v>0.09030175703529458</v>
       </c>
       <c r="C39">
-        <v>9894.977746338489</v>
+        <v>9783.048249472278</v>
       </c>
       <c r="D39">
-        <v>14245.22074633849</v>
+        <v>14274.53024947228</v>
       </c>
       <c r="E39">
-        <v>5176.443</v>
+        <v>5317.682000000001</v>
       </c>
       <c r="F39">
-        <v>5225.843</v>
+        <v>5367.082</v>
       </c>
       <c r="G39">
         <v>875.6</v>
@@ -4491,28 +4491,28 @@
         <v>851.8</v>
       </c>
       <c r="M39">
-        <v>302.0537254</v>
+        <v>310.2173396000001</v>
       </c>
       <c r="N39">
-        <v>549.7462745999999</v>
+        <v>541.5826603999999</v>
       </c>
       <c r="O39">
-        <v>109.94925492</v>
+        <v>108.31653208</v>
       </c>
       <c r="P39">
-        <v>439.7970196799999</v>
+        <v>433.2661283199999</v>
       </c>
       <c r="Q39">
-        <v>682.99701968</v>
+        <v>676.4661283199999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1163246337777138</v>
+        <v>0.1173073500569267</v>
       </c>
       <c r="T39">
-        <v>1.374656379759464</v>
+        <v>1.393811349170172</v>
       </c>
       <c r="U39">
         <v>0.0578</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.820028122056725</v>
+        <v>2.745816855686812</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09030175703529458</v>
+        <v>0.09021019479062944</v>
       </c>
       <c r="C40">
-        <v>9783.048249472278</v>
+        <v>9671.239609716002</v>
       </c>
       <c r="D40">
-        <v>14274.53024947228</v>
+        <v>14303.960609716</v>
       </c>
       <c r="E40">
-        <v>5317.682000000001</v>
+        <v>5458.921</v>
       </c>
       <c r="F40">
-        <v>5367.082</v>
+        <v>5508.321</v>
       </c>
       <c r="G40">
         <v>875.6</v>
@@ -4573,28 +4573,28 @@
         <v>851.8</v>
       </c>
       <c r="M40">
-        <v>310.2173396000001</v>
+        <v>318.3809538</v>
       </c>
       <c r="N40">
-        <v>541.5826603999999</v>
+        <v>533.4190461999999</v>
       </c>
       <c r="O40">
-        <v>108.31653208</v>
+        <v>106.68380924</v>
       </c>
       <c r="P40">
-        <v>433.2661283199999</v>
+        <v>426.73523696</v>
       </c>
       <c r="Q40">
-        <v>676.4661283199999</v>
+        <v>669.93523696</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1173073500569267</v>
+        <v>0.1183222865420155</v>
       </c>
       <c r="T40">
-        <v>1.393811349170172</v>
+        <v>1.413594350364838</v>
       </c>
       <c r="U40">
         <v>0.0578</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.745816855686812</v>
+        <v>2.675411295284586</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09021019479062944</v>
+        <v>0.09011863254596431</v>
       </c>
       <c r="C41">
-        <v>9671.239609716002</v>
+        <v>9559.552576141614</v>
       </c>
       <c r="D41">
-        <v>14303.960609716</v>
+        <v>14333.51257614161</v>
       </c>
       <c r="E41">
-        <v>5458.921</v>
+        <v>5600.160000000001</v>
       </c>
       <c r="F41">
-        <v>5508.321</v>
+        <v>5649.56</v>
       </c>
       <c r="G41">
         <v>875.6</v>
@@ -4655,28 +4655,28 @@
         <v>851.8</v>
       </c>
       <c r="M41">
-        <v>318.3809538</v>
+        <v>326.544568</v>
       </c>
       <c r="N41">
-        <v>533.4190461999999</v>
+        <v>525.2554319999999</v>
       </c>
       <c r="O41">
-        <v>106.68380924</v>
+        <v>105.0510864</v>
       </c>
       <c r="P41">
-        <v>426.73523696</v>
+        <v>420.2043456</v>
       </c>
       <c r="Q41">
-        <v>669.93523696</v>
+        <v>663.4043455999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1183222865420155</v>
+        <v>0.1193710542432738</v>
       </c>
       <c r="T41">
-        <v>1.413594350364838</v>
+        <v>1.434036784932659</v>
       </c>
       <c r="U41">
         <v>0.0578</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.675411295284586</v>
+        <v>2.608526012902471</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09011863254596431</v>
+        <v>0.09002707030129917</v>
       </c>
       <c r="C42">
-        <v>9559.552576141614</v>
+        <v>9447.987904024212</v>
       </c>
       <c r="D42">
-        <v>14333.51257614161</v>
+        <v>14363.18690402421</v>
       </c>
       <c r="E42">
-        <v>5600.160000000001</v>
+        <v>5741.399</v>
       </c>
       <c r="F42">
-        <v>5649.56</v>
+        <v>5790.799</v>
       </c>
       <c r="G42">
         <v>875.6</v>
@@ -4737,28 +4737,28 @@
         <v>851.8</v>
       </c>
       <c r="M42">
-        <v>326.544568</v>
+        <v>334.7081822</v>
       </c>
       <c r="N42">
-        <v>525.2554319999999</v>
+        <v>517.0918177999999</v>
       </c>
       <c r="O42">
-        <v>105.0510864</v>
+        <v>103.41836356</v>
       </c>
       <c r="P42">
-        <v>420.2043456</v>
+        <v>413.67345424</v>
       </c>
       <c r="Q42">
-        <v>663.4043455999999</v>
+        <v>656.87345424</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1193710542432738</v>
+        <v>0.1204553733920325</v>
       </c>
       <c r="T42">
-        <v>1.434036784932659</v>
+        <v>1.455172183384135</v>
       </c>
       <c r="U42">
         <v>0.0578</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.608526012902471</v>
+        <v>2.544903427221923</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09002707030129917</v>
+        <v>0.09111150805663404</v>
       </c>
       <c r="C43">
-        <v>9447.987904024212</v>
+        <v>8962.995565552512</v>
       </c>
       <c r="D43">
-        <v>14363.18690402421</v>
+        <v>14019.43356555251</v>
       </c>
       <c r="E43">
-        <v>5741.399</v>
+        <v>5882.638000000001</v>
       </c>
       <c r="F43">
-        <v>5790.799</v>
+        <v>5932.038</v>
       </c>
       <c r="G43">
         <v>875.6</v>
@@ -4819,45 +4819,45 @@
         <v>851.8</v>
       </c>
       <c r="M43">
-        <v>334.7081822</v>
+        <v>363.6339294000001</v>
       </c>
       <c r="N43">
-        <v>517.0918177999999</v>
+        <v>488.1660705999999</v>
       </c>
       <c r="O43">
-        <v>103.41836356</v>
+        <v>97.63321411999999</v>
       </c>
       <c r="P43">
-        <v>413.67345424</v>
+        <v>390.5328564799999</v>
       </c>
       <c r="Q43">
-        <v>656.87345424</v>
+        <v>633.73285648</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1204553733920325</v>
+        <v>0.1215770828562656</v>
       </c>
       <c r="T43">
-        <v>1.455172183384135</v>
+        <v>1.477036388678766</v>
       </c>
       <c r="U43">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V43">
         <v>0.2</v>
       </c>
       <c r="W43">
-        <v>0.04624</v>
+        <v>0.04904</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y43">
-        <v>2.544903427221923</v>
+        <v>2.342465680816637</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09111150805663404</v>
+        <v>0.0910479458119689</v>
       </c>
       <c r="C44">
-        <v>8962.995565552512</v>
+        <v>8841.450424585657</v>
       </c>
       <c r="D44">
-        <v>14019.43356555251</v>
+        <v>14039.12742458566</v>
       </c>
       <c r="E44">
-        <v>5882.638</v>
+        <v>6023.877</v>
       </c>
       <c r="F44">
-        <v>5932.038</v>
+        <v>6073.277</v>
       </c>
       <c r="G44">
         <v>875.6</v>
@@ -4901,28 +4901,28 @@
         <v>851.8</v>
       </c>
       <c r="M44">
-        <v>363.6339294</v>
+        <v>372.2918801</v>
       </c>
       <c r="N44">
-        <v>488.1660706</v>
+        <v>479.5081198999999</v>
       </c>
       <c r="O44">
-        <v>97.63321411999999</v>
+        <v>95.90162398</v>
       </c>
       <c r="P44">
-        <v>390.53285648</v>
+        <v>383.6064959199999</v>
       </c>
       <c r="Q44">
-        <v>633.73285648</v>
+        <v>626.80649592</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1215770828562656</v>
+        <v>0.1227381505473139</v>
       </c>
       <c r="T44">
-        <v>1.477036388678765</v>
+        <v>1.499667759071453</v>
       </c>
       <c r="U44">
         <v>0.0613</v>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.342465680816637</v>
+        <v>2.287989734751134</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.0910479458119689</v>
+        <v>0.09196998356730376</v>
       </c>
       <c r="C45">
-        <v>8841.450424585657</v>
+        <v>8419.84300040038</v>
       </c>
       <c r="D45">
-        <v>14039.12742458566</v>
+        <v>13758.75900040038</v>
       </c>
       <c r="E45">
-        <v>6023.877</v>
+        <v>6165.116</v>
       </c>
       <c r="F45">
-        <v>6073.277</v>
+        <v>6214.516</v>
       </c>
       <c r="G45">
         <v>875.6</v>
@@ -4983,45 +4983,45 @@
         <v>851.8</v>
       </c>
       <c r="M45">
-        <v>372.2918801</v>
+        <v>398.3504756</v>
       </c>
       <c r="N45">
-        <v>479.5081198999999</v>
+        <v>453.4495244</v>
       </c>
       <c r="O45">
-        <v>95.90162398</v>
+        <v>90.68990488</v>
       </c>
       <c r="P45">
-        <v>383.6064959199999</v>
+        <v>362.75961952</v>
       </c>
       <c r="Q45">
-        <v>626.80649592</v>
+        <v>605.95961952</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1227381505473139</v>
+        <v>0.1239406849416138</v>
       </c>
       <c r="T45">
-        <v>1.499667759071453</v>
+        <v>1.523107392692451</v>
       </c>
       <c r="U45">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V45">
         <v>0.2</v>
       </c>
       <c r="W45">
-        <v>0.04904</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y45">
-        <v>2.287989734751134</v>
+        <v>2.138318019369775</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09196998356730376</v>
+        <v>0.09192882132263862</v>
       </c>
       <c r="C46">
-        <v>8419.84300040038</v>
+        <v>8290.881387682883</v>
       </c>
       <c r="D46">
-        <v>13758.75900040038</v>
+        <v>13771.03638768288</v>
       </c>
       <c r="E46">
-        <v>6165.116</v>
+        <v>6306.355</v>
       </c>
       <c r="F46">
-        <v>6214.516</v>
+        <v>6355.755</v>
       </c>
       <c r="G46">
         <v>875.6</v>
@@ -5065,28 +5065,28 @@
         <v>851.8</v>
       </c>
       <c r="M46">
-        <v>398.3504756</v>
+        <v>407.4038955</v>
       </c>
       <c r="N46">
-        <v>453.4495244</v>
+        <v>444.3961044999999</v>
       </c>
       <c r="O46">
-        <v>90.68990488</v>
+        <v>88.87922089999999</v>
       </c>
       <c r="P46">
-        <v>362.75961952</v>
+        <v>355.5168835999999</v>
       </c>
       <c r="Q46">
-        <v>605.95961952</v>
+        <v>598.7168836</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1239406849416138</v>
+        <v>0.1251869478593429</v>
       </c>
       <c r="T46">
-        <v>1.523107392692451</v>
+        <v>1.54739937662694</v>
       </c>
       <c r="U46">
         <v>0.0641</v>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.138318019369775</v>
+        <v>2.090799841161558</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09192882132263862</v>
+        <v>0.09188765907797349</v>
       </c>
       <c r="C47">
-        <v>8290.881387682883</v>
+        <v>8161.941705557178</v>
       </c>
       <c r="D47">
-        <v>13771.03638768288</v>
+        <v>13783.33570555718</v>
       </c>
       <c r="E47">
-        <v>6306.355</v>
+        <v>6447.594</v>
       </c>
       <c r="F47">
-        <v>6355.755</v>
+        <v>6496.994</v>
       </c>
       <c r="G47">
         <v>875.6</v>
@@ -5147,28 +5147,28 @@
         <v>851.8</v>
       </c>
       <c r="M47">
-        <v>407.4038955</v>
+        <v>416.4573154</v>
       </c>
       <c r="N47">
-        <v>444.3961044999999</v>
+        <v>435.3426845999999</v>
       </c>
       <c r="O47">
-        <v>88.87922089999999</v>
+        <v>87.06853691999999</v>
       </c>
       <c r="P47">
-        <v>355.5168835999999</v>
+        <v>348.2741476799999</v>
       </c>
       <c r="Q47">
-        <v>598.7168836</v>
+        <v>591.47414768</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1251869478593429</v>
+        <v>0.1264793686629138</v>
       </c>
       <c r="T47">
-        <v>1.54739937662694</v>
+        <v>1.572591063670114</v>
       </c>
       <c r="U47">
         <v>0.0641</v>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.090799841161558</v>
+        <v>2.045347670701524</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09188765907797349</v>
+        <v>0.09184649683330834</v>
       </c>
       <c r="C48">
-        <v>8161.941705557178</v>
+        <v>8033.024012836378</v>
       </c>
       <c r="D48">
-        <v>13783.33570555718</v>
+        <v>13795.65701283638</v>
       </c>
       <c r="E48">
-        <v>6447.594</v>
+        <v>6588.833000000001</v>
       </c>
       <c r="F48">
-        <v>6496.994</v>
+        <v>6638.233</v>
       </c>
       <c r="G48">
         <v>875.6</v>
@@ -5229,28 +5229,28 @@
         <v>851.8</v>
       </c>
       <c r="M48">
-        <v>416.4573154</v>
+        <v>425.5107353</v>
       </c>
       <c r="N48">
-        <v>435.3426845999999</v>
+        <v>426.2892646999999</v>
       </c>
       <c r="O48">
-        <v>87.06853691999999</v>
+        <v>85.25785293999999</v>
       </c>
       <c r="P48">
-        <v>348.2741476799999</v>
+        <v>341.03141176</v>
       </c>
       <c r="Q48">
-        <v>591.47414768</v>
+        <v>584.23141176</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1264793686629138</v>
+        <v>0.1278205600628459</v>
       </c>
       <c r="T48">
-        <v>1.572591063670114</v>
+        <v>1.59873338041303</v>
       </c>
       <c r="U48">
         <v>0.0641</v>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.045347670701524</v>
+        <v>2.001829635154683</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09184649683330834</v>
+        <v>0.0962981345886432</v>
       </c>
       <c r="C49">
-        <v>8033.024012836378</v>
+        <v>6675.63578042881</v>
       </c>
       <c r="D49">
-        <v>13795.65701283638</v>
+        <v>12579.50778042881</v>
       </c>
       <c r="E49">
-        <v>6588.833000000001</v>
+        <v>6730.072000000001</v>
       </c>
       <c r="F49">
-        <v>6638.233</v>
+        <v>6779.472000000001</v>
       </c>
       <c r="G49">
         <v>875.6</v>
@@ -5311,45 +5311,45 @@
         <v>851.8</v>
       </c>
       <c r="M49">
-        <v>425.5107353</v>
+        <v>513.8839776000001</v>
       </c>
       <c r="N49">
-        <v>426.2892646999999</v>
+        <v>337.9160223999999</v>
       </c>
       <c r="O49">
-        <v>85.25785293999999</v>
+        <v>67.58320447999998</v>
       </c>
       <c r="P49">
-        <v>341.03141176</v>
+        <v>270.3328179199999</v>
       </c>
       <c r="Q49">
-        <v>584.23141176</v>
+        <v>513.53281792</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1278205600628459</v>
+        <v>0.1292133357473907</v>
       </c>
       <c r="T49">
-        <v>1.59873338041303</v>
+        <v>1.625881170876827</v>
       </c>
       <c r="U49">
-        <v>0.0641</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V49">
         <v>0.2</v>
       </c>
       <c r="W49">
-        <v>0.05128000000000001</v>
+        <v>0.06064000000000001</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y49">
-        <v>2.001829635154683</v>
+        <v>1.657572598348316</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09629813458864318</v>
+        <v>0.09635057234397806</v>
       </c>
       <c r="C50">
-        <v>6675.635780428815</v>
+        <v>6521.347647241266</v>
       </c>
       <c r="D50">
-        <v>12579.50778042881</v>
+        <v>12566.45864724126</v>
       </c>
       <c r="E50">
-        <v>6730.072</v>
+        <v>6871.311</v>
       </c>
       <c r="F50">
-        <v>6779.472</v>
+        <v>6920.710999999999</v>
       </c>
       <c r="G50">
         <v>875.6</v>
@@ -5393,28 +5393,28 @@
         <v>851.8</v>
       </c>
       <c r="M50">
-        <v>513.8839776</v>
+        <v>524.5898938</v>
       </c>
       <c r="N50">
-        <v>337.9160224</v>
+        <v>327.2101061999999</v>
       </c>
       <c r="O50">
-        <v>67.58320447999999</v>
+        <v>65.44202123999999</v>
       </c>
       <c r="P50">
-        <v>270.33281792</v>
+        <v>261.76808496</v>
       </c>
       <c r="Q50">
-        <v>513.5328179200001</v>
+        <v>504.96808496</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1292133357473907</v>
+        <v>0.1306607300862315</v>
       </c>
       <c r="T50">
-        <v>1.625881170876827</v>
+        <v>1.654093580574499</v>
       </c>
       <c r="U50">
         <v>0.07580000000000001</v>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>1.657572598348316</v>
+        <v>1.623744586137126</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09635057234397806</v>
+        <v>0.09640301009931292</v>
       </c>
       <c r="C51">
-        <v>6521.347647241266</v>
+        <v>6367.086558581394</v>
       </c>
       <c r="D51">
-        <v>12566.45864724126</v>
+        <v>12553.43655858139</v>
       </c>
       <c r="E51">
-        <v>6871.311</v>
+        <v>7012.55</v>
       </c>
       <c r="F51">
-        <v>6920.710999999999</v>
+        <v>7061.95</v>
       </c>
       <c r="G51">
         <v>875.6</v>
@@ -5475,28 +5475,28 @@
         <v>851.8</v>
       </c>
       <c r="M51">
-        <v>524.5898938</v>
+        <v>535.2958100000001</v>
       </c>
       <c r="N51">
-        <v>327.2101061999999</v>
+        <v>316.5041899999999</v>
       </c>
       <c r="O51">
-        <v>65.44202123999999</v>
+        <v>63.30083799999998</v>
       </c>
       <c r="P51">
-        <v>261.76808496</v>
+        <v>253.2033519999999</v>
       </c>
       <c r="Q51">
-        <v>504.96808496</v>
+        <v>496.4033519999999</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1306607300862315</v>
+        <v>0.1321660201986258</v>
       </c>
       <c r="T51">
-        <v>1.654093580574499</v>
+        <v>1.683434486660078</v>
       </c>
       <c r="U51">
         <v>0.07580000000000001</v>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>1.623744586137126</v>
+        <v>1.591269694414383</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09640301009931292</v>
+        <v>0.09645544785464778</v>
       </c>
       <c r="C52">
-        <v>6367.086558581394</v>
+        <v>6212.852430460929</v>
       </c>
       <c r="D52">
-        <v>12553.43655858139</v>
+        <v>12540.44143046093</v>
       </c>
       <c r="E52">
-        <v>7012.55</v>
+        <v>7153.789000000001</v>
       </c>
       <c r="F52">
-        <v>7061.95</v>
+        <v>7203.189</v>
       </c>
       <c r="G52">
         <v>875.6</v>
@@ -5557,28 +5557,28 @@
         <v>851.8</v>
       </c>
       <c r="M52">
-        <v>535.2958100000001</v>
+        <v>546.0017262000001</v>
       </c>
       <c r="N52">
-        <v>316.5041899999999</v>
+        <v>305.7982737999998</v>
       </c>
       <c r="O52">
-        <v>63.30083799999998</v>
+        <v>61.15965475999997</v>
       </c>
       <c r="P52">
-        <v>253.2033519999999</v>
+        <v>244.6386190399999</v>
       </c>
       <c r="Q52">
-        <v>496.4033519999999</v>
+        <v>487.8386190399999</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1321660201986258</v>
+        <v>0.133732750723771</v>
       </c>
       <c r="T52">
-        <v>1.683434486660078</v>
+        <v>1.713972980749149</v>
       </c>
       <c r="U52">
         <v>0.07580000000000001</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.591269694414383</v>
+        <v>1.560068327857238</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09645544785464778</v>
+        <v>0.09650788560998264</v>
       </c>
       <c r="C53">
-        <v>6212.852430460929</v>
+        <v>6058.645179239031</v>
       </c>
       <c r="D53">
-        <v>12540.44143046093</v>
+        <v>12527.47317923903</v>
       </c>
       <c r="E53">
-        <v>7153.789000000001</v>
+        <v>7295.028</v>
       </c>
       <c r="F53">
-        <v>7203.189</v>
+        <v>7344.428</v>
       </c>
       <c r="G53">
         <v>875.6</v>
@@ -5639,28 +5639,28 @@
         <v>851.8</v>
       </c>
       <c r="M53">
-        <v>546.0017262000001</v>
+        <v>556.7076424000001</v>
       </c>
       <c r="N53">
-        <v>305.7982737999998</v>
+        <v>295.0923575999999</v>
       </c>
       <c r="O53">
-        <v>61.15965475999997</v>
+        <v>59.01847151999998</v>
       </c>
       <c r="P53">
-        <v>244.6386190399999</v>
+        <v>236.0738860799999</v>
       </c>
       <c r="Q53">
-        <v>487.8386190399999</v>
+        <v>479.27388608</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.133732750723771</v>
+        <v>0.1353647616874638</v>
       </c>
       <c r="T53">
-        <v>1.713972980749149</v>
+        <v>1.745783912091932</v>
       </c>
       <c r="U53">
         <v>0.07580000000000001</v>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>1.560068327857238</v>
+        <v>1.530067013859984</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09650788560998264</v>
+        <v>0.0965603233653175</v>
       </c>
       <c r="C54">
-        <v>6058.645179239031</v>
+        <v>5904.464721620464</v>
       </c>
       <c r="D54">
-        <v>12527.47317923903</v>
+        <v>12514.53172162046</v>
       </c>
       <c r="E54">
-        <v>7295.028</v>
+        <v>7436.267000000001</v>
       </c>
       <c r="F54">
-        <v>7344.428</v>
+        <v>7485.667</v>
       </c>
       <c r="G54">
         <v>875.6</v>
@@ -5721,28 +5721,28 @@
         <v>851.8</v>
       </c>
       <c r="M54">
-        <v>556.7076424000001</v>
+        <v>567.4135586000001</v>
       </c>
       <c r="N54">
-        <v>295.0923575999999</v>
+        <v>284.3864413999999</v>
       </c>
       <c r="O54">
-        <v>59.01847151999998</v>
+        <v>56.87728827999997</v>
       </c>
       <c r="P54">
-        <v>236.0738860799999</v>
+        <v>227.5091531199999</v>
       </c>
       <c r="Q54">
-        <v>479.27388608</v>
+        <v>470.7091531199999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1353647616874638</v>
+        <v>0.1370662199262074</v>
       </c>
       <c r="T54">
-        <v>1.745783912091932</v>
+        <v>1.7789485000876</v>
       </c>
       <c r="U54">
         <v>0.07580000000000001</v>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>1.530067013859984</v>
+        <v>1.50119782491923</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.0965603233653175</v>
+        <v>0.116151535262161</v>
       </c>
       <c r="C55">
-        <v>5904.464721620464</v>
+        <v>2278.229383809133</v>
       </c>
       <c r="D55">
-        <v>12514.53172162046</v>
+        <v>9029.535383809132</v>
       </c>
       <c r="E55">
-        <v>7436.267000000001</v>
+        <v>7577.506</v>
       </c>
       <c r="F55">
-        <v>7485.667</v>
+        <v>7626.906</v>
       </c>
       <c r="G55">
         <v>875.6</v>
@@ -5803,45 +5803,45 @@
         <v>851.8</v>
       </c>
       <c r="M55">
-        <v>567.4135586000001</v>
+        <v>904.5510516000001</v>
       </c>
       <c r="N55">
-        <v>284.3864413999999</v>
+        <v>-52.7510516000001</v>
       </c>
       <c r="O55">
-        <v>56.87728827999997</v>
+        <v>-10.55021032000002</v>
       </c>
       <c r="P55">
-        <v>227.5091531199999</v>
+        <v>-42.20084128000008</v>
       </c>
       <c r="Q55">
-        <v>470.7091531199999</v>
+        <v>200.99915872</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1370662199262074</v>
+        <v>0.1394986077083087</v>
       </c>
       <c r="T55">
-        <v>1.7789485000876</v>
+        <v>1.826360265361751</v>
       </c>
       <c r="U55">
-        <v>0.07580000000000001</v>
+        <v>0.1186</v>
       </c>
       <c r="V55">
-        <v>0.2</v>
+        <v>0.1883365230725912</v>
       </c>
       <c r="W55">
-        <v>0.06064000000000001</v>
+        <v>0.09626328836359069</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y55">
-        <v>1.50119782491923</v>
+        <v>0.9416826153629557</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.116151535262161</v>
+        <v>0.116879535262161</v>
       </c>
       <c r="C56">
-        <v>2278.229383809133</v>
+        <v>2044.509450511408</v>
       </c>
       <c r="D56">
-        <v>9029.535383809132</v>
+        <v>8937.054450511409</v>
       </c>
       <c r="E56">
-        <v>7577.506</v>
+        <v>7718.745000000001</v>
       </c>
       <c r="F56">
-        <v>7626.906</v>
+        <v>7768.145</v>
       </c>
       <c r="G56">
         <v>875.6</v>
@@ -5885,37 +5885,37 @@
         <v>851.8</v>
       </c>
       <c r="M56">
-        <v>904.5510516000001</v>
+        <v>921.3019970000001</v>
       </c>
       <c r="N56">
-        <v>-52.7510516000001</v>
+        <v>-69.50199700000019</v>
       </c>
       <c r="O56">
-        <v>-10.55021032000002</v>
+        <v>-13.90039940000004</v>
       </c>
       <c r="P56">
-        <v>-42.20084128000008</v>
+        <v>-55.60159760000015</v>
       </c>
       <c r="Q56">
-        <v>200.99915872</v>
+        <v>187.5984023999999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1394986077083087</v>
+        <v>0.1415807989907155</v>
       </c>
       <c r="T56">
-        <v>1.826360265361751</v>
+        <v>1.866946049036457</v>
       </c>
       <c r="U56">
         <v>0.1186</v>
       </c>
       <c r="V56">
-        <v>0.1883365230725912</v>
+        <v>0.1849122226530895</v>
       </c>
       <c r="W56">
-        <v>0.09626328836359069</v>
+        <v>0.09666941039334359</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.9416826153629557</v>
+        <v>0.9245611132654473</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.116879535262161</v>
+        <v>0.117607535262161</v>
       </c>
       <c r="C57">
-        <v>2044.509450511408</v>
+        <v>1812.664699788743</v>
       </c>
       <c r="D57">
-        <v>8937.054450511409</v>
+        <v>8846.448699788743</v>
       </c>
       <c r="E57">
-        <v>7718.745000000001</v>
+        <v>7859.984000000001</v>
       </c>
       <c r="F57">
-        <v>7768.145</v>
+        <v>7909.384000000001</v>
       </c>
       <c r="G57">
         <v>875.6</v>
@@ -5967,37 +5967,37 @@
         <v>851.8</v>
       </c>
       <c r="M57">
-        <v>921.3019970000001</v>
+        <v>938.0529424000002</v>
       </c>
       <c r="N57">
-        <v>-69.50199700000019</v>
+        <v>-86.25294240000028</v>
       </c>
       <c r="O57">
-        <v>-13.90039940000004</v>
+        <v>-17.25058848000006</v>
       </c>
       <c r="P57">
-        <v>-55.60159760000015</v>
+        <v>-69.00235392000022</v>
       </c>
       <c r="Q57">
-        <v>187.5984023999999</v>
+        <v>174.1976460799998</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1415807989907155</v>
+        <v>0.1437576353314136</v>
       </c>
       <c r="T57">
-        <v>1.866946049036457</v>
+        <v>1.909376641060013</v>
       </c>
       <c r="U57">
         <v>0.1186</v>
       </c>
       <c r="V57">
-        <v>0.1849122226530895</v>
+        <v>0.1816102186771414</v>
       </c>
       <c r="W57">
-        <v>0.09666941039334359</v>
+        <v>0.09706102806489103</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.9245611132654473</v>
+        <v>0.9080510933857071</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.117607535262161</v>
+        <v>0.118335535262161</v>
       </c>
       <c r="C58">
-        <v>1812.664699788743</v>
+        <v>1582.638671056277</v>
       </c>
       <c r="D58">
-        <v>8846.448699788743</v>
+        <v>8757.661671056278</v>
       </c>
       <c r="E58">
-        <v>7859.984000000001</v>
+        <v>8001.223000000001</v>
       </c>
       <c r="F58">
-        <v>7909.384000000001</v>
+        <v>8050.623000000001</v>
       </c>
       <c r="G58">
         <v>875.6</v>
@@ -6049,37 +6049,37 @@
         <v>851.8</v>
       </c>
       <c r="M58">
-        <v>938.0529424000002</v>
+        <v>954.8038878000001</v>
       </c>
       <c r="N58">
-        <v>-86.25294240000028</v>
+        <v>-103.0038878000001</v>
       </c>
       <c r="O58">
-        <v>-17.25058848000006</v>
+        <v>-20.60077756000003</v>
       </c>
       <c r="P58">
-        <v>-69.00235392000022</v>
+        <v>-82.40311024000012</v>
       </c>
       <c r="Q58">
-        <v>174.1976460799998</v>
+        <v>160.7968897599999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1437576353314136</v>
+        <v>0.1460357198740047</v>
       </c>
       <c r="T58">
-        <v>1.909376641060013</v>
+        <v>1.953780748991641</v>
       </c>
       <c r="U58">
         <v>0.1186</v>
       </c>
       <c r="V58">
-        <v>0.1816102186771414</v>
+        <v>0.1784240744898232</v>
       </c>
       <c r="W58">
-        <v>0.09706102806489103</v>
+        <v>0.09743890476550697</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.9080510933857071</v>
+        <v>0.8921203724491159</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.118335535262161</v>
+        <v>0.119063535262161</v>
       </c>
       <c r="C59">
-        <v>1582.638671056277</v>
+        <v>1354.377147863603</v>
       </c>
       <c r="D59">
-        <v>8757.661671056278</v>
+        <v>8670.639147863603</v>
       </c>
       <c r="E59">
-        <v>8001.223000000001</v>
+        <v>8142.462000000001</v>
       </c>
       <c r="F59">
-        <v>8050.623000000001</v>
+        <v>8191.862000000001</v>
       </c>
       <c r="G59">
         <v>875.6</v>
@@ -6131,37 +6131,37 @@
         <v>851.8</v>
       </c>
       <c r="M59">
-        <v>954.8038878000001</v>
+        <v>971.5548332000002</v>
       </c>
       <c r="N59">
-        <v>-103.0038878000001</v>
+        <v>-119.7548332000002</v>
       </c>
       <c r="O59">
-        <v>-20.60077756000003</v>
+        <v>-23.95096664000005</v>
       </c>
       <c r="P59">
-        <v>-82.40311024000012</v>
+        <v>-95.80386656000019</v>
       </c>
       <c r="Q59">
-        <v>160.7968897599999</v>
+        <v>147.3961334399999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1460357198740047</v>
+        <v>0.1484222846329095</v>
       </c>
       <c r="T59">
-        <v>1.953780748991641</v>
+        <v>2.000299338253346</v>
       </c>
       <c r="U59">
         <v>0.1186</v>
       </c>
       <c r="V59">
-        <v>0.1784240744898232</v>
+        <v>0.1753477973434469</v>
       </c>
       <c r="W59">
-        <v>0.09743890476550697</v>
+        <v>0.0978037512350672</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.8921203724491159</v>
+        <v>0.8767389867172345</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.119063535262161</v>
+        <v>0.119791535262161</v>
       </c>
       <c r="C60">
-        <v>1354.377147863604</v>
+        <v>1127.828047494962</v>
       </c>
       <c r="D60">
-        <v>8670.639147863603</v>
+        <v>8585.329047494961</v>
       </c>
       <c r="E60">
-        <v>8142.462</v>
+        <v>8283.700999999999</v>
       </c>
       <c r="F60">
-        <v>8191.861999999999</v>
+        <v>8333.100999999999</v>
       </c>
       <c r="G60">
         <v>875.6</v>
@@ -6213,37 +6213,37 @@
         <v>851.8</v>
       </c>
       <c r="M60">
-        <v>971.5548332</v>
+        <v>988.3057785999999</v>
       </c>
       <c r="N60">
-        <v>-119.7548332</v>
+        <v>-136.5057786</v>
       </c>
       <c r="O60">
-        <v>-23.95096664</v>
+        <v>-27.30115572</v>
       </c>
       <c r="P60">
-        <v>-95.80386656</v>
+        <v>-109.20462288</v>
       </c>
       <c r="Q60">
-        <v>147.39613344</v>
+        <v>133.9953771200001</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1484222846329095</v>
+        <v>0.1509252671849317</v>
       </c>
       <c r="T60">
-        <v>2.000299338253346</v>
+        <v>2.049087126991233</v>
       </c>
       <c r="U60">
         <v>0.1186</v>
       </c>
       <c r="V60">
-        <v>0.175347797343447</v>
+        <v>0.1723758007783038</v>
       </c>
       <c r="W60">
-        <v>0.0978037512350672</v>
+        <v>0.09815623002769318</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.8767389867172347</v>
+        <v>0.8618790038915189</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.119791535262161</v>
+        <v>0.120519535262161</v>
       </c>
       <c r="C61">
-        <v>1127.828047494962</v>
+        <v>902.9413170233092</v>
       </c>
       <c r="D61">
-        <v>8585.329047494961</v>
+        <v>8501.681317023309</v>
       </c>
       <c r="E61">
-        <v>8283.700999999999</v>
+        <v>8424.940000000001</v>
       </c>
       <c r="F61">
-        <v>8333.100999999999</v>
+        <v>8474.34</v>
       </c>
       <c r="G61">
         <v>875.6</v>
@@ -6295,37 +6295,37 @@
         <v>851.8</v>
       </c>
       <c r="M61">
-        <v>988.3057785999999</v>
+        <v>1005.056724</v>
       </c>
       <c r="N61">
-        <v>-136.5057786</v>
+        <v>-153.2567240000002</v>
       </c>
       <c r="O61">
-        <v>-27.30115572</v>
+        <v>-30.65134480000004</v>
       </c>
       <c r="P61">
-        <v>-109.20462288</v>
+        <v>-122.6053792000002</v>
       </c>
       <c r="Q61">
-        <v>133.9953771200001</v>
+        <v>120.5946207999999</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1509252671849317</v>
+        <v>0.153553398864555</v>
       </c>
       <c r="T61">
-        <v>2.049087126991233</v>
+        <v>2.100314305166014</v>
       </c>
       <c r="U61">
         <v>0.1186</v>
       </c>
       <c r="V61">
-        <v>0.1723758007783038</v>
+        <v>0.169502870765332</v>
       </c>
       <c r="W61">
-        <v>0.09815623002769318</v>
+        <v>0.09849695952723163</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.8618790038915189</v>
+        <v>0.8475143538266601</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.120519535262161</v>
+        <v>0.121247535262161</v>
       </c>
       <c r="C62">
-        <v>902.9413170233092</v>
+        <v>679.6688353822337</v>
       </c>
       <c r="D62">
-        <v>8501.681317023309</v>
+        <v>8419.647835382233</v>
       </c>
       <c r="E62">
-        <v>8424.940000000001</v>
+        <v>8566.179</v>
       </c>
       <c r="F62">
-        <v>8474.34</v>
+        <v>8615.579</v>
       </c>
       <c r="G62">
         <v>875.6</v>
@@ -6377,37 +6377,37 @@
         <v>851.8</v>
       </c>
       <c r="M62">
-        <v>1005.056724</v>
+        <v>1021.8076694</v>
       </c>
       <c r="N62">
-        <v>-153.2567240000002</v>
+        <v>-170.0076694000001</v>
       </c>
       <c r="O62">
-        <v>-30.65134480000004</v>
+        <v>-34.00153388000001</v>
       </c>
       <c r="P62">
-        <v>-122.6053792000002</v>
+        <v>-136.00613552</v>
       </c>
       <c r="Q62">
-        <v>120.5946207999999</v>
+        <v>107.19386448</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.153553398864555</v>
+        <v>0.1563163065277487</v>
       </c>
       <c r="T62">
-        <v>2.100314305166014</v>
+        <v>2.154168518118988</v>
       </c>
       <c r="U62">
         <v>0.1186</v>
       </c>
       <c r="V62">
-        <v>0.169502870765332</v>
+        <v>0.1667241351790151</v>
       </c>
       <c r="W62">
-        <v>0.09849695952723163</v>
+        <v>0.09882651756776881</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.8475143538266601</v>
+        <v>0.8336206758950756</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.121247535262161</v>
+        <v>0.121975535262161</v>
       </c>
       <c r="C63">
-        <v>679.6688353822337</v>
+        <v>457.9643210532104</v>
       </c>
       <c r="D63">
-        <v>8419.647835382233</v>
+        <v>8339.182321053209</v>
       </c>
       <c r="E63">
-        <v>8566.179</v>
+        <v>8707.418</v>
       </c>
       <c r="F63">
-        <v>8615.579</v>
+        <v>8756.817999999999</v>
       </c>
       <c r="G63">
         <v>875.6</v>
@@ -6459,37 +6459,37 @@
         <v>851.8</v>
       </c>
       <c r="M63">
-        <v>1021.8076694</v>
+        <v>1038.5586148</v>
       </c>
       <c r="N63">
-        <v>-170.0076694000001</v>
+        <v>-186.7586148</v>
       </c>
       <c r="O63">
-        <v>-34.00153388000001</v>
+        <v>-37.35172296000001</v>
       </c>
       <c r="P63">
-        <v>-136.00613552</v>
+        <v>-149.40689184</v>
       </c>
       <c r="Q63">
-        <v>107.19386448</v>
+        <v>93.79310816000003</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1563163065277487</v>
+        <v>0.1592246303837421</v>
       </c>
       <c r="T63">
-        <v>2.154168518118988</v>
+        <v>2.210857163332646</v>
       </c>
       <c r="U63">
         <v>0.1186</v>
       </c>
       <c r="V63">
-        <v>0.1667241351790151</v>
+        <v>0.1640350362245149</v>
       </c>
       <c r="W63">
-        <v>0.09882651756776881</v>
+        <v>0.09914544470377254</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.8336206758950756</v>
+        <v>0.8201751811225744</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.121975535262161</v>
+        <v>0.122703535262161</v>
       </c>
       <c r="C64">
-        <v>457.9643210532104</v>
+        <v>237.7832449960933</v>
       </c>
       <c r="D64">
-        <v>8339.182321053209</v>
+        <v>8260.240244996094</v>
       </c>
       <c r="E64">
-        <v>8707.418</v>
+        <v>8848.657000000001</v>
       </c>
       <c r="F64">
-        <v>8756.817999999999</v>
+        <v>8898.057000000001</v>
       </c>
       <c r="G64">
         <v>875.6</v>
@@ -6541,37 +6541,37 @@
         <v>851.8</v>
       </c>
       <c r="M64">
-        <v>1038.5586148</v>
+        <v>1055.3095602</v>
       </c>
       <c r="N64">
-        <v>-186.7586148</v>
+        <v>-203.5095602000001</v>
       </c>
       <c r="O64">
-        <v>-37.35172296000001</v>
+        <v>-40.70191204000002</v>
       </c>
       <c r="P64">
-        <v>-149.40689184</v>
+        <v>-162.8076481600001</v>
       </c>
       <c r="Q64">
-        <v>93.79310816000003</v>
+        <v>80.39235183999995</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1592246303837421</v>
+        <v>0.162290160934654</v>
       </c>
       <c r="T64">
-        <v>2.210857163332646</v>
+        <v>2.270610059638933</v>
       </c>
       <c r="U64">
         <v>0.1186</v>
       </c>
       <c r="V64">
-        <v>0.1640350362245149</v>
+        <v>0.1614313054907924</v>
       </c>
       <c r="W64">
-        <v>0.09914544470377254</v>
+        <v>0.09945424716879203</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.8201751811225744</v>
+        <v>0.807156527453962</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.122703535262161</v>
+        <v>0.1780371273989671</v>
       </c>
       <c r="C65">
-        <v>237.7832449960933</v>
+        <v>-3359.888707374706</v>
       </c>
       <c r="D65">
-        <v>8260.240244996094</v>
+        <v>4803.807292625293</v>
       </c>
       <c r="E65">
-        <v>8848.657000000001</v>
+        <v>8989.896000000001</v>
       </c>
       <c r="F65">
-        <v>8898.057000000001</v>
+        <v>9039.296</v>
       </c>
       <c r="G65">
         <v>875.6</v>
@@ -6623,45 +6623,45 @@
         <v>851.8</v>
       </c>
       <c r="M65">
-        <v>1055.3095602</v>
+        <v>1815.0906368</v>
       </c>
       <c r="N65">
-        <v>-203.5095602000001</v>
+        <v>-963.2906368000001</v>
       </c>
       <c r="O65">
-        <v>-40.70191204000002</v>
+        <v>-192.65812736</v>
       </c>
       <c r="P65">
-        <v>-162.8076481600001</v>
+        <v>-770.6325094400001</v>
       </c>
       <c r="Q65">
-        <v>80.39235183999995</v>
+        <v>-527.4325094400001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.162290160934654</v>
+        <v>0.1710748657850782</v>
       </c>
       <c r="T65">
-        <v>2.270610059638933</v>
+        <v>2.441840308136241</v>
       </c>
       <c r="U65">
-        <v>0.1186</v>
+        <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.1614313054907924</v>
+        <v>0.09385757192838823</v>
       </c>
       <c r="W65">
-        <v>0.09945424716879203</v>
+        <v>0.1819533995567796</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y65">
-        <v>0.807156527453962</v>
+        <v>0.4692878596419411</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1780371273989671</v>
+        <v>0.1795871273989672</v>
       </c>
       <c r="C66">
-        <v>-3359.888707374706</v>
+        <v>-3556.782548377196</v>
       </c>
       <c r="D66">
-        <v>4803.807292625293</v>
+        <v>4748.152451622804</v>
       </c>
       <c r="E66">
-        <v>8989.896000000001</v>
+        <v>9131.135</v>
       </c>
       <c r="F66">
-        <v>9039.296</v>
+        <v>9180.535</v>
       </c>
       <c r="G66">
         <v>875.6</v>
@@ -6705,37 +6705,37 @@
         <v>851.8</v>
       </c>
       <c r="M66">
-        <v>1815.0906368</v>
+        <v>1843.451428</v>
       </c>
       <c r="N66">
-        <v>-963.2906368000001</v>
+        <v>-991.6514280000001</v>
       </c>
       <c r="O66">
-        <v>-192.65812736</v>
+        <v>-198.3302856</v>
       </c>
       <c r="P66">
-        <v>-770.6325094400001</v>
+        <v>-793.3211424000001</v>
       </c>
       <c r="Q66">
-        <v>-527.4325094400001</v>
+        <v>-550.1211424000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1710748657850782</v>
+        <v>0.1746541476646519</v>
       </c>
       <c r="T66">
-        <v>2.441840308136241</v>
+        <v>2.51160717408299</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.09385757192838823</v>
+        <v>0.0924136092833361</v>
       </c>
       <c r="W66">
-        <v>0.1819533995567796</v>
+        <v>0.1822433472559061</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.4692878596419411</v>
+        <v>0.4620680464166805</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1795871273989672</v>
+        <v>0.1811371273989671</v>
       </c>
       <c r="C67">
-        <v>-3556.782548377196</v>
+        <v>-3752.401572849854</v>
       </c>
       <c r="D67">
-        <v>4748.152451622804</v>
+        <v>4693.772427150145</v>
       </c>
       <c r="E67">
-        <v>9131.135</v>
+        <v>9272.374</v>
       </c>
       <c r="F67">
-        <v>9180.535</v>
+        <v>9321.773999999999</v>
       </c>
       <c r="G67">
         <v>875.6</v>
@@ -6787,37 +6787,37 @@
         <v>851.8</v>
       </c>
       <c r="M67">
-        <v>1843.451428</v>
+        <v>1871.8122192</v>
       </c>
       <c r="N67">
-        <v>-991.6514280000001</v>
+        <v>-1020.0122192</v>
       </c>
       <c r="O67">
-        <v>-198.3302856</v>
+        <v>-204.00244384</v>
       </c>
       <c r="P67">
-        <v>-793.3211424000001</v>
+        <v>-816.0097753599999</v>
       </c>
       <c r="Q67">
-        <v>-550.1211424000001</v>
+        <v>-572.8097753599999</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1746541476646519</v>
+        <v>0.1784439755371416</v>
       </c>
       <c r="T67">
-        <v>2.51160717408299</v>
+        <v>2.585477973320725</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.0924136092833361</v>
+        <v>0.09101340308207345</v>
       </c>
       <c r="W67">
-        <v>0.1822433472559061</v>
+        <v>0.1825245086611196</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.4620680464166805</v>
+        <v>0.4550670154103672</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1811371273989671</v>
+        <v>0.1826871273989671</v>
       </c>
       <c r="C68">
-        <v>-3752.401572849854</v>
+        <v>-3946.789085791313</v>
       </c>
       <c r="D68">
-        <v>4693.772427150145</v>
+        <v>4640.623914208687</v>
       </c>
       <c r="E68">
-        <v>9272.374</v>
+        <v>9413.613000000001</v>
       </c>
       <c r="F68">
-        <v>9321.773999999999</v>
+        <v>9463.013000000001</v>
       </c>
       <c r="G68">
         <v>875.6</v>
@@ -6869,37 +6869,37 @@
         <v>851.8</v>
       </c>
       <c r="M68">
-        <v>1871.8122192</v>
+        <v>1900.1730104</v>
       </c>
       <c r="N68">
-        <v>-1020.0122192</v>
+        <v>-1048.3730104</v>
       </c>
       <c r="O68">
-        <v>-204.00244384</v>
+        <v>-209.6746020800001</v>
       </c>
       <c r="P68">
-        <v>-816.0097753599999</v>
+        <v>-838.6984083200002</v>
       </c>
       <c r="Q68">
-        <v>-572.8097753599999</v>
+        <v>-595.4984083200002</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1784439755371416</v>
+        <v>0.1824634899473581</v>
       </c>
       <c r="T68">
-        <v>2.585477973320725</v>
+        <v>2.663825790694081</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.09101340308207345</v>
+        <v>0.08965499408084844</v>
       </c>
       <c r="W68">
-        <v>0.1825245086611196</v>
+        <v>0.1827972771885656</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.4550670154103672</v>
+        <v>0.4482749704042422</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1826871273989671</v>
+        <v>0.1842371273989671</v>
       </c>
       <c r="C69">
-        <v>-3946.789085791313</v>
+        <v>-4139.986452756655</v>
       </c>
       <c r="D69">
-        <v>4640.623914208687</v>
+        <v>4588.665547243345</v>
       </c>
       <c r="E69">
-        <v>9413.613000000001</v>
+        <v>9554.852000000001</v>
       </c>
       <c r="F69">
-        <v>9463.013000000001</v>
+        <v>9604.252</v>
       </c>
       <c r="G69">
         <v>875.6</v>
@@ -6951,37 +6951,37 @@
         <v>851.8</v>
       </c>
       <c r="M69">
-        <v>1900.1730104</v>
+        <v>1928.5338016</v>
       </c>
       <c r="N69">
-        <v>-1048.3730104</v>
+        <v>-1076.7338016</v>
       </c>
       <c r="O69">
-        <v>-209.6746020800001</v>
+        <v>-215.34676032</v>
       </c>
       <c r="P69">
-        <v>-838.6984083200002</v>
+        <v>-861.3870412800001</v>
       </c>
       <c r="Q69">
-        <v>-595.4984083200002</v>
+        <v>-618.18704128</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1824634899473581</v>
+        <v>0.186734224008213</v>
       </c>
       <c r="T69">
-        <v>2.663825790694081</v>
+        <v>2.747070346653271</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.08965499408084844</v>
+        <v>0.08833653828554186</v>
       </c>
       <c r="W69">
-        <v>0.1827972771885656</v>
+        <v>0.1830620231122632</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.4482749704042422</v>
+        <v>0.4416826914277093</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1842371273989671</v>
+        <v>0.1857871273989672</v>
       </c>
       <c r="C70">
-        <v>-4139.986452756655</v>
+        <v>-4332.033207229368</v>
       </c>
       <c r="D70">
-        <v>4588.665547243345</v>
+        <v>4537.857792770632</v>
       </c>
       <c r="E70">
-        <v>9554.852000000001</v>
+        <v>9696.091</v>
       </c>
       <c r="F70">
-        <v>9604.252</v>
+        <v>9745.491</v>
       </c>
       <c r="G70">
         <v>875.6</v>
@@ -7033,37 +7033,37 @@
         <v>851.8</v>
       </c>
       <c r="M70">
-        <v>1928.5338016</v>
+        <v>1956.8945928</v>
       </c>
       <c r="N70">
-        <v>-1076.7338016</v>
+        <v>-1105.0945928</v>
       </c>
       <c r="O70">
-        <v>-215.34676032</v>
+        <v>-221.01891856</v>
       </c>
       <c r="P70">
-        <v>-861.3870412800001</v>
+        <v>-884.0756742400001</v>
       </c>
       <c r="Q70">
-        <v>-618.18704128</v>
+        <v>-640.8756742400001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.186734224008213</v>
+        <v>0.1912804892988006</v>
       </c>
       <c r="T70">
-        <v>2.747070346653271</v>
+        <v>2.835685519125958</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.08833653828554186</v>
+        <v>0.08705629860024416</v>
       </c>
       <c r="W70">
-        <v>0.1830620231122632</v>
+        <v>0.183319095241071</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.4416826914277093</v>
+        <v>0.4352814930012208</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1857871273989672</v>
+        <v>0.1873371273989672</v>
       </c>
       <c r="C71">
-        <v>-4332.033207229368</v>
+        <v>-4522.967150938152</v>
       </c>
       <c r="D71">
-        <v>4537.857792770632</v>
+        <v>4488.162849061849</v>
       </c>
       <c r="E71">
-        <v>9696.091</v>
+        <v>9837.330000000002</v>
       </c>
       <c r="F71">
-        <v>9745.491</v>
+        <v>9886.730000000001</v>
       </c>
       <c r="G71">
         <v>875.6</v>
@@ -7115,37 +7115,37 @@
         <v>851.8</v>
       </c>
       <c r="M71">
-        <v>1956.8945928</v>
+        <v>1985.255384</v>
       </c>
       <c r="N71">
-        <v>-1105.0945928</v>
+        <v>-1133.455384</v>
       </c>
       <c r="O71">
-        <v>-221.01891856</v>
+        <v>-226.6910768000001</v>
       </c>
       <c r="P71">
-        <v>-884.0756742400001</v>
+        <v>-906.7643072000003</v>
       </c>
       <c r="Q71">
-        <v>-640.8756742400001</v>
+        <v>-663.5643072000003</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1912804892988006</v>
+        <v>0.1961298389420939</v>
       </c>
       <c r="T71">
-        <v>2.835685519125958</v>
+        <v>2.93020836976349</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.08705629860024416</v>
+        <v>0.08581263719166923</v>
       </c>
       <c r="W71">
-        <v>0.183319095241071</v>
+        <v>0.1835688224519128</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.4352814930012208</v>
+        <v>0.4290631859583461</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1873371273989672</v>
+        <v>0.1888871273989671</v>
       </c>
       <c r="C72">
-        <v>-4522.967150938152</v>
+        <v>-4712.824447653612</v>
       </c>
       <c r="D72">
-        <v>4488.162849061849</v>
+        <v>4439.544552346389</v>
       </c>
       <c r="E72">
-        <v>9837.330000000002</v>
+        <v>9978.569000000001</v>
       </c>
       <c r="F72">
-        <v>9886.730000000001</v>
+        <v>10027.969</v>
       </c>
       <c r="G72">
         <v>875.6</v>
@@ -7197,37 +7197,37 @@
         <v>851.8</v>
       </c>
       <c r="M72">
-        <v>1985.255384</v>
+        <v>2013.6161752</v>
       </c>
       <c r="N72">
-        <v>-1133.455384</v>
+        <v>-1161.8161752</v>
       </c>
       <c r="O72">
-        <v>-226.6910768000001</v>
+        <v>-232.3632350400001</v>
       </c>
       <c r="P72">
-        <v>-906.7643072000003</v>
+        <v>-929.4529401600003</v>
       </c>
       <c r="Q72">
-        <v>-663.5643072000003</v>
+        <v>-686.2529401600002</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1961298389420939</v>
+        <v>0.2013136264918213</v>
       </c>
       <c r="T72">
-        <v>2.93020836976349</v>
+        <v>3.031250037686368</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.08581263719166923</v>
+        <v>0.08460400849882882</v>
       </c>
       <c r="W72">
-        <v>0.1835688224519128</v>
+        <v>0.1838115150934352</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.4290631859583461</v>
+        <v>0.423020042494144</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1888871273989671</v>
+        <v>0.1904371273989671</v>
       </c>
       <c r="C73">
-        <v>-4712.82444765361</v>
+        <v>-4901.63971095394</v>
       </c>
       <c r="D73">
-        <v>4439.544552346389</v>
+        <v>4391.968289046058</v>
       </c>
       <c r="E73">
-        <v>9978.569</v>
+        <v>10119.808</v>
       </c>
       <c r="F73">
-        <v>10027.969</v>
+        <v>10169.208</v>
       </c>
       <c r="G73">
         <v>875.6</v>
@@ -7279,37 +7279,37 @@
         <v>851.8</v>
       </c>
       <c r="M73">
-        <v>2013.6161752</v>
+        <v>2041.9769664</v>
       </c>
       <c r="N73">
-        <v>-1161.8161752</v>
+        <v>-1190.1769664</v>
       </c>
       <c r="O73">
-        <v>-232.36323504</v>
+        <v>-238.03539328</v>
       </c>
       <c r="P73">
-        <v>-929.4529401599999</v>
+        <v>-952.1415731199999</v>
       </c>
       <c r="Q73">
-        <v>-686.2529401599999</v>
+        <v>-708.9415731199998</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2013136264918212</v>
+        <v>0.2068676845808148</v>
       </c>
       <c r="T73">
-        <v>3.031250037686368</v>
+        <v>3.139508967603738</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.08460400849882883</v>
+        <v>0.08342895282523399</v>
       </c>
       <c r="W73">
-        <v>0.1838115150934352</v>
+        <v>0.184047466272693</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.4230200424941442</v>
+        <v>0.41714476412617</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1904371273989671</v>
+        <v>0.1919871273989671</v>
       </c>
       <c r="C74">
-        <v>-4901.63971095394</v>
+        <v>-5089.446086407204</v>
       </c>
       <c r="D74">
-        <v>4391.968289046058</v>
+        <v>4345.400913592795</v>
       </c>
       <c r="E74">
-        <v>10119.808</v>
+        <v>10261.047</v>
       </c>
       <c r="F74">
-        <v>10169.208</v>
+        <v>10310.447</v>
       </c>
       <c r="G74">
         <v>875.6</v>
@@ -7361,37 +7361,37 @@
         <v>851.8</v>
       </c>
       <c r="M74">
-        <v>2041.9769664</v>
+        <v>2070.3377576</v>
       </c>
       <c r="N74">
-        <v>-1190.1769664</v>
+        <v>-1218.5377576</v>
       </c>
       <c r="O74">
-        <v>-238.03539328</v>
+        <v>-243.7075515200001</v>
       </c>
       <c r="P74">
-        <v>-952.1415731199999</v>
+        <v>-974.8302060800003</v>
       </c>
       <c r="Q74">
-        <v>-708.9415731199998</v>
+        <v>-731.6302060800002</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2068676845808148</v>
+        <v>0.2128331543801043</v>
       </c>
       <c r="T74">
-        <v>3.139508967603738</v>
+        <v>3.255787077514987</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.08342895282523399</v>
+        <v>0.08228609045776503</v>
       </c>
       <c r="W74">
-        <v>0.184047466272693</v>
+        <v>0.1842769530360808</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.41714476412617</v>
+        <v>0.411430452288825</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1919871273989671</v>
+        <v>0.1935371273989671</v>
       </c>
       <c r="C75">
-        <v>-5089.446086407204</v>
+        <v>-5276.275328580247</v>
       </c>
       <c r="D75">
-        <v>4345.400913592795</v>
+        <v>4299.810671419752</v>
       </c>
       <c r="E75">
-        <v>10261.047</v>
+        <v>10402.286</v>
       </c>
       <c r="F75">
-        <v>10310.447</v>
+        <v>10451.686</v>
       </c>
       <c r="G75">
         <v>875.6</v>
@@ -7443,37 +7443,37 @@
         <v>851.8</v>
       </c>
       <c r="M75">
-        <v>2070.3377576</v>
+        <v>2098.6985488</v>
       </c>
       <c r="N75">
-        <v>-1218.5377576</v>
+        <v>-1246.8985488</v>
       </c>
       <c r="O75">
-        <v>-243.7075515200001</v>
+        <v>-249.37970976</v>
       </c>
       <c r="P75">
-        <v>-974.8302060800003</v>
+        <v>-997.5188390400001</v>
       </c>
       <c r="Q75">
-        <v>-731.6302060800002</v>
+        <v>-754.3188390400001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2128331543801043</v>
+        <v>0.2192575064716467</v>
       </c>
       <c r="T75">
-        <v>3.255787077514987</v>
+        <v>3.38100965741941</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.08228609045776503</v>
+        <v>0.08117411626238982</v>
       </c>
       <c r="W75">
-        <v>0.1842769530360808</v>
+        <v>0.1845002374545121</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.411430452288825</v>
+        <v>0.4058705813119491</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1935371273989671</v>
+        <v>0.1950871273989671</v>
       </c>
       <c r="C76">
-        <v>-5276.275328580247</v>
+        <v>-5462.157873250307</v>
       </c>
       <c r="D76">
-        <v>4299.810671419752</v>
+        <v>4255.167126749692</v>
       </c>
       <c r="E76">
-        <v>10402.286</v>
+        <v>10543.525</v>
       </c>
       <c r="F76">
-        <v>10451.686</v>
+        <v>10592.925</v>
       </c>
       <c r="G76">
         <v>875.6</v>
@@ -7525,37 +7525,37 @@
         <v>851.8</v>
       </c>
       <c r="M76">
-        <v>2098.6985488</v>
+        <v>2127.05934</v>
       </c>
       <c r="N76">
-        <v>-1246.8985488</v>
+        <v>-1275.25934</v>
       </c>
       <c r="O76">
-        <v>-249.37970976</v>
+        <v>-255.051868</v>
       </c>
       <c r="P76">
-        <v>-997.5188390400001</v>
+        <v>-1020.207472</v>
       </c>
       <c r="Q76">
-        <v>-754.3188390400001</v>
+        <v>-777.0074719999998</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2192575064716467</v>
+        <v>0.2261958067305126</v>
       </c>
       <c r="T76">
-        <v>3.38100965741941</v>
+        <v>3.516250043716187</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.08117411626238982</v>
+        <v>0.08009179471222463</v>
       </c>
       <c r="W76">
-        <v>0.1845002374545121</v>
+        <v>0.1847175676217853</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.4058705813119491</v>
+        <v>0.4004589735611231</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1950871273989671</v>
+        <v>0.1966371273989671</v>
       </c>
       <c r="C77">
-        <v>-5462.157873250307</v>
+        <v>-5647.122905164299</v>
       </c>
       <c r="D77">
-        <v>4255.167126749692</v>
+        <v>4211.441094835701</v>
       </c>
       <c r="E77">
-        <v>10543.525</v>
+        <v>10684.764</v>
       </c>
       <c r="F77">
-        <v>10592.925</v>
+        <v>10734.164</v>
       </c>
       <c r="G77">
         <v>875.6</v>
@@ -7607,37 +7607,37 @@
         <v>851.8</v>
       </c>
       <c r="M77">
-        <v>2127.05934</v>
+        <v>2155.4201312</v>
       </c>
       <c r="N77">
-        <v>-1275.25934</v>
+        <v>-1303.6201312</v>
       </c>
       <c r="O77">
-        <v>-255.051868</v>
+        <v>-260.72402624</v>
       </c>
       <c r="P77">
-        <v>-1020.207472</v>
+        <v>-1042.89610496</v>
       </c>
       <c r="Q77">
-        <v>-777.0074719999998</v>
+        <v>-799.69610496</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2261958067305126</v>
+        <v>0.2337122986776173</v>
       </c>
       <c r="T77">
-        <v>3.516250043716187</v>
+        <v>3.662760462204361</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.08009179471222463</v>
+        <v>0.07903795530811641</v>
       </c>
       <c r="W77">
-        <v>0.1847175676217853</v>
+        <v>0.1849291785741302</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.4004589735611231</v>
+        <v>0.395189776540582</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1966371273989671</v>
+        <v>0.1981871273989671</v>
       </c>
       <c r="C78">
-        <v>-5647.122905164299</v>
+        <v>-5831.198421662868</v>
       </c>
       <c r="D78">
-        <v>4211.441094835701</v>
+        <v>4168.604578337132</v>
       </c>
       <c r="E78">
-        <v>10684.764</v>
+        <v>10826.003</v>
       </c>
       <c r="F78">
-        <v>10734.164</v>
+        <v>10875.403</v>
       </c>
       <c r="G78">
         <v>875.6</v>
@@ -7689,37 +7689,37 @@
         <v>851.8</v>
       </c>
       <c r="M78">
-        <v>2155.4201312</v>
+        <v>2183.7809224</v>
       </c>
       <c r="N78">
-        <v>-1303.6201312</v>
+        <v>-1331.9809224</v>
       </c>
       <c r="O78">
-        <v>-260.72402624</v>
+        <v>-266.39618448</v>
       </c>
       <c r="P78">
-        <v>-1042.89610496</v>
+        <v>-1065.58473792</v>
       </c>
       <c r="Q78">
-        <v>-799.69610496</v>
+        <v>-822.3847379200001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2337122986776173</v>
+        <v>0.2418823986201224</v>
       </c>
       <c r="T78">
-        <v>3.662760462204361</v>
+        <v>3.822010917082811</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.07903795530811641</v>
+        <v>0.07801148835606293</v>
       </c>
       <c r="W78">
-        <v>0.1849291785741302</v>
+        <v>0.1851352931381026</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.395189776540582</v>
+        <v>0.3900574417803147</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1981871273989671</v>
+        <v>0.1997371273989672</v>
       </c>
       <c r="C79">
-        <v>-5831.198421662868</v>
+        <v>-6014.411292460628</v>
       </c>
       <c r="D79">
-        <v>4168.604578337132</v>
+        <v>4126.630707539372</v>
       </c>
       <c r="E79">
-        <v>10826.003</v>
+        <v>10967.242</v>
       </c>
       <c r="F79">
-        <v>10875.403</v>
+        <v>11016.642</v>
       </c>
       <c r="G79">
         <v>875.6</v>
@@ -7771,37 +7771,37 @@
         <v>851.8</v>
       </c>
       <c r="M79">
-        <v>2183.7809224</v>
+        <v>2212.1417136</v>
       </c>
       <c r="N79">
-        <v>-1331.9809224</v>
+        <v>-1360.3417136</v>
       </c>
       <c r="O79">
-        <v>-266.39618448</v>
+        <v>-272.06834272</v>
       </c>
       <c r="P79">
-        <v>-1065.58473792</v>
+        <v>-1088.27337088</v>
       </c>
       <c r="Q79">
-        <v>-822.3847379200001</v>
+        <v>-845.0733708800001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2418823986201224</v>
+        <v>0.2507952349210371</v>
       </c>
       <c r="T79">
-        <v>3.822010917082811</v>
+        <v>3.995738686041121</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.07801148835606293</v>
+        <v>0.07701134106944675</v>
       </c>
       <c r="W79">
-        <v>0.1851352931381026</v>
+        <v>0.1853361227132551</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3900574417803147</v>
+        <v>0.3850567053472338</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1997371273989672</v>
+        <v>0.2012871273989671</v>
       </c>
       <c r="C80">
-        <v>-6014.411292460628</v>
+        <v>-6196.787315850826</v>
       </c>
       <c r="D80">
-        <v>4126.630707539372</v>
+        <v>4085.493684149174</v>
       </c>
       <c r="E80">
-        <v>10967.242</v>
+        <v>11108.481</v>
       </c>
       <c r="F80">
-        <v>11016.642</v>
+        <v>11157.881</v>
       </c>
       <c r="G80">
         <v>875.6</v>
@@ -7853,37 +7853,37 @@
         <v>851.8</v>
       </c>
       <c r="M80">
-        <v>2212.1417136</v>
+        <v>2240.5025048</v>
       </c>
       <c r="N80">
-        <v>-1360.3417136</v>
+        <v>-1388.7025048</v>
       </c>
       <c r="O80">
-        <v>-272.06834272</v>
+        <v>-277.74050096</v>
       </c>
       <c r="P80">
-        <v>-1088.27337088</v>
+        <v>-1110.96200384</v>
       </c>
       <c r="Q80">
-        <v>-845.0733708800001</v>
+        <v>-867.7620038399998</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2507952349210371</v>
+        <v>0.2605569127744198</v>
       </c>
       <c r="T80">
-        <v>3.995738686041121</v>
+        <v>4.186011956804985</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.07701134106944675</v>
+        <v>0.07603651396730188</v>
       </c>
       <c r="W80">
-        <v>0.1853361227132551</v>
+        <v>0.1855318679953658</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3850567053472338</v>
+        <v>0.3801825698365093</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2012871273989671</v>
+        <v>0.2028371273989671</v>
       </c>
       <c r="C81">
-        <v>-6196.787315850826</v>
+        <v>-6378.351271581474</v>
       </c>
       <c r="D81">
-        <v>4085.493684149174</v>
+        <v>4045.168728418527</v>
       </c>
       <c r="E81">
-        <v>11108.481</v>
+        <v>11249.72</v>
       </c>
       <c r="F81">
-        <v>11157.881</v>
+        <v>11299.12</v>
       </c>
       <c r="G81">
         <v>875.6</v>
@@ -7935,37 +7935,37 @@
         <v>851.8</v>
       </c>
       <c r="M81">
-        <v>2240.5025048</v>
+        <v>2268.863296</v>
       </c>
       <c r="N81">
-        <v>-1388.7025048</v>
+        <v>-1417.063296</v>
       </c>
       <c r="O81">
-        <v>-277.74050096</v>
+        <v>-283.4126592000001</v>
       </c>
       <c r="P81">
-        <v>-1110.96200384</v>
+        <v>-1133.6506368</v>
       </c>
       <c r="Q81">
-        <v>-867.7620038399998</v>
+        <v>-890.4506368000004</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2605569127744198</v>
+        <v>0.2712947584131408</v>
       </c>
       <c r="T81">
-        <v>4.186011956804985</v>
+        <v>4.395312554645234</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.07603651396730188</v>
+        <v>0.07508605754271058</v>
       </c>
       <c r="W81">
-        <v>0.1855318679953658</v>
+        <v>0.1857227196454237</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3801825698365093</v>
+        <v>0.3754302877135528</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2028371273989671</v>
+        <v>0.2043871273989671</v>
       </c>
       <c r="C82">
-        <v>-6378.351271581474</v>
+        <v>-6559.126970630665</v>
       </c>
       <c r="D82">
-        <v>4045.168728418527</v>
+        <v>4005.632029369336</v>
       </c>
       <c r="E82">
-        <v>11249.72</v>
+        <v>11390.959</v>
       </c>
       <c r="F82">
-        <v>11299.12</v>
+        <v>11440.359</v>
       </c>
       <c r="G82">
         <v>875.6</v>
@@ -8017,37 +8017,37 @@
         <v>851.8</v>
       </c>
       <c r="M82">
-        <v>2268.863296</v>
+        <v>2297.2240872</v>
       </c>
       <c r="N82">
-        <v>-1417.063296</v>
+        <v>-1445.4240872</v>
       </c>
       <c r="O82">
-        <v>-283.4126592000001</v>
+        <v>-289.0848174400001</v>
       </c>
       <c r="P82">
-        <v>-1133.6506368</v>
+        <v>-1156.33926976</v>
       </c>
       <c r="Q82">
-        <v>-890.4506368000004</v>
+        <v>-913.1392697600002</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2712947584131408</v>
+        <v>0.2831629035927798</v>
       </c>
       <c r="T82">
-        <v>4.395312554645234</v>
+        <v>4.626644794363404</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.07508605754271058</v>
+        <v>0.07415906917798575</v>
       </c>
       <c r="W82">
-        <v>0.1857227196454237</v>
+        <v>0.1859088589090605</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3754302877135528</v>
+        <v>0.3707953458899288</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2043871273989671</v>
+        <v>0.2059371273989671</v>
       </c>
       <c r="C83">
-        <v>-6559.126970630665</v>
+        <v>-6739.137302091193</v>
       </c>
       <c r="D83">
-        <v>4005.632029369336</v>
+        <v>3966.860697908807</v>
       </c>
       <c r="E83">
-        <v>11390.959</v>
+        <v>11532.198</v>
       </c>
       <c r="F83">
-        <v>11440.359</v>
+        <v>11581.598</v>
       </c>
       <c r="G83">
         <v>875.6</v>
@@ -8099,37 +8099,37 @@
         <v>851.8</v>
       </c>
       <c r="M83">
-        <v>2297.2240872</v>
+        <v>2325.5848784</v>
       </c>
       <c r="N83">
-        <v>-1445.4240872</v>
+        <v>-1473.7848784</v>
       </c>
       <c r="O83">
-        <v>-289.0848174400001</v>
+        <v>-294.75697568</v>
       </c>
       <c r="P83">
-        <v>-1156.33926976</v>
+        <v>-1179.02790272</v>
       </c>
       <c r="Q83">
-        <v>-913.1392697600002</v>
+        <v>-935.8279027199999</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2831629035927798</v>
+        <v>0.2963497315701565</v>
       </c>
       <c r="T83">
-        <v>4.626644794363404</v>
+        <v>4.883680616272482</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.07415906917798575</v>
+        <v>0.0732546902855713</v>
       </c>
       <c r="W83">
-        <v>0.1859088589090605</v>
+        <v>0.1860904581906573</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3707953458899288</v>
+        <v>0.3662734514278565</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2059371273989671</v>
+        <v>0.2074871273989672</v>
       </c>
       <c r="C84">
-        <v>-6739.137302091193</v>
+        <v>-6918.404277358432</v>
       </c>
       <c r="D84">
-        <v>3966.860697908807</v>
+        <v>3928.832722641569</v>
       </c>
       <c r="E84">
-        <v>11532.198</v>
+        <v>11673.437</v>
       </c>
       <c r="F84">
-        <v>11581.598</v>
+        <v>11722.837</v>
       </c>
       <c r="G84">
         <v>875.6</v>
@@ -8181,37 +8181,37 @@
         <v>851.8</v>
       </c>
       <c r="M84">
-        <v>2325.5848784</v>
+        <v>2353.9456696</v>
       </c>
       <c r="N84">
-        <v>-1473.7848784</v>
+        <v>-1502.1456696</v>
       </c>
       <c r="O84">
-        <v>-294.75697568</v>
+        <v>-300.4291339200001</v>
       </c>
       <c r="P84">
-        <v>-1179.02790272</v>
+        <v>-1201.71653568</v>
       </c>
       <c r="Q84">
-        <v>-935.8279027199999</v>
+        <v>-958.5165356800001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2963497315701565</v>
+        <v>0.3110879510742834</v>
       </c>
       <c r="T84">
-        <v>4.883680616272482</v>
+        <v>5.170955946641453</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.0732546902855713</v>
+        <v>0.07237210365562466</v>
       </c>
       <c r="W84">
-        <v>0.1860904581906573</v>
+        <v>0.1862676815859506</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3662734514278565</v>
+        <v>0.3618605182781233</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2074871273989672</v>
+        <v>0.2090371273989672</v>
       </c>
       <c r="C85">
-        <v>-6918.404277358432</v>
+        <v>-7096.949071800714</v>
       </c>
       <c r="D85">
-        <v>3928.832722641569</v>
+        <v>3891.526928199287</v>
       </c>
       <c r="E85">
-        <v>11673.437</v>
+        <v>11814.676</v>
       </c>
       <c r="F85">
-        <v>11722.837</v>
+        <v>11864.076</v>
       </c>
       <c r="G85">
         <v>875.6</v>
@@ -8263,37 +8263,37 @@
         <v>851.8</v>
       </c>
       <c r="M85">
-        <v>2353.9456696</v>
+        <v>2382.3064608</v>
       </c>
       <c r="N85">
-        <v>-1502.1456696</v>
+        <v>-1530.5064608</v>
       </c>
       <c r="O85">
-        <v>-300.4291339200001</v>
+        <v>-306.1012921600001</v>
       </c>
       <c r="P85">
-        <v>-1201.71653568</v>
+        <v>-1224.40516864</v>
       </c>
       <c r="Q85">
-        <v>-958.5165356800001</v>
+        <v>-981.2051686400002</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3110879510742834</v>
+        <v>0.3276684480164261</v>
       </c>
       <c r="T85">
-        <v>5.170955946641453</v>
+        <v>5.494140693306544</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.07237210365562466</v>
+        <v>0.07151053099305769</v>
       </c>
       <c r="W85">
-        <v>0.1862676815859506</v>
+        <v>0.186440685376594</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3618605182781233</v>
+        <v>0.3575526549652884</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2090371273989672</v>
+        <v>0.2105871273989671</v>
       </c>
       <c r="C86">
-        <v>-7096.949071800712</v>
+        <v>-7274.792064078002</v>
       </c>
       <c r="D86">
-        <v>3891.526928199287</v>
+        <v>3854.922935921996</v>
       </c>
       <c r="E86">
-        <v>11814.676</v>
+        <v>11955.915</v>
       </c>
       <c r="F86">
-        <v>11864.076</v>
+        <v>12005.315</v>
       </c>
       <c r="G86">
         <v>875.6</v>
@@ -8345,37 +8345,37 @@
         <v>851.8</v>
       </c>
       <c r="M86">
-        <v>2382.3064608</v>
+        <v>2410.667252</v>
       </c>
       <c r="N86">
-        <v>-1530.5064608</v>
+        <v>-1558.867252</v>
       </c>
       <c r="O86">
-        <v>-306.10129216</v>
+        <v>-311.7734504</v>
       </c>
       <c r="P86">
-        <v>-1224.40516864</v>
+        <v>-1247.0938016</v>
       </c>
       <c r="Q86">
-        <v>-981.20516864</v>
+        <v>-1003.8938016</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.327668448016426</v>
+        <v>0.3464596778841877</v>
       </c>
       <c r="T86">
-        <v>5.494140693306541</v>
+        <v>5.860416739526976</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.07151053099305769</v>
+        <v>0.0706692306284335</v>
       </c>
       <c r="W86">
-        <v>0.186440685376594</v>
+        <v>0.1866096184898106</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3575526549652885</v>
+        <v>0.3533461531421674</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2105871273989671</v>
+        <v>0.2121371273989672</v>
       </c>
       <c r="C87">
-        <v>-7274.792064078002</v>
+        <v>-7451.952873262238</v>
       </c>
       <c r="D87">
-        <v>3854.922935921996</v>
+        <v>3819.001126737761</v>
       </c>
       <c r="E87">
-        <v>11955.915</v>
+        <v>12097.154</v>
       </c>
       <c r="F87">
-        <v>12005.315</v>
+        <v>12146.554</v>
       </c>
       <c r="G87">
         <v>875.6</v>
@@ -8427,37 +8427,37 @@
         <v>851.8</v>
       </c>
       <c r="M87">
-        <v>2410.667252</v>
+        <v>2439.0280432</v>
       </c>
       <c r="N87">
-        <v>-1558.867252</v>
+        <v>-1587.2280432</v>
       </c>
       <c r="O87">
-        <v>-311.7734504</v>
+        <v>-317.44560864</v>
       </c>
       <c r="P87">
-        <v>-1247.0938016</v>
+        <v>-1269.78243456</v>
       </c>
       <c r="Q87">
-        <v>-1003.8938016</v>
+        <v>-1026.58243456</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3464596778841877</v>
+        <v>0.3679353691616297</v>
       </c>
       <c r="T87">
-        <v>5.860416739526976</v>
+        <v>6.279017935207476</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.0706692306284335</v>
+        <v>0.06984749538856798</v>
       </c>
       <c r="W87">
-        <v>0.1866096184898106</v>
+        <v>0.1867746229259756</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3533461531421674</v>
+        <v>0.3492374769428399</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2121371273989672</v>
+        <v>0.2136871273989671</v>
       </c>
       <c r="C88">
-        <v>-7451.952873262238</v>
+        <v>-7628.450393901383</v>
       </c>
       <c r="D88">
-        <v>3819.001126737761</v>
+        <v>3783.742606098617</v>
       </c>
       <c r="E88">
-        <v>12097.154</v>
+        <v>12238.393</v>
       </c>
       <c r="F88">
-        <v>12146.554</v>
+        <v>12287.793</v>
       </c>
       <c r="G88">
         <v>875.6</v>
@@ -8509,37 +8509,37 @@
         <v>851.8</v>
       </c>
       <c r="M88">
-        <v>2439.0280432</v>
+        <v>2467.3888344</v>
       </c>
       <c r="N88">
-        <v>-1587.2280432</v>
+        <v>-1615.5888344</v>
       </c>
       <c r="O88">
-        <v>-317.44560864</v>
+        <v>-323.1177668800001</v>
       </c>
       <c r="P88">
-        <v>-1269.78243456</v>
+        <v>-1292.47106752</v>
       </c>
       <c r="Q88">
-        <v>-1026.58243456</v>
+        <v>-1049.27106752</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3679353691616297</v>
+        <v>0.3927150129432935</v>
       </c>
       <c r="T88">
-        <v>6.279017935207476</v>
+        <v>6.762019314838819</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.06984749538856798</v>
+        <v>0.06904465061398674</v>
       </c>
       <c r="W88">
-        <v>0.1867746229259756</v>
+        <v>0.1869358341567114</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3492374769428399</v>
+        <v>0.3452232530699337</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2136871273989671</v>
+        <v>0.2152371273989671</v>
       </c>
       <c r="C89">
-        <v>-7628.450393901383</v>
+        <v>-7804.302829158954</v>
       </c>
       <c r="D89">
-        <v>3783.742606098617</v>
+        <v>3749.129170841045</v>
       </c>
       <c r="E89">
-        <v>12238.393</v>
+        <v>12379.632</v>
       </c>
       <c r="F89">
-        <v>12287.793</v>
+        <v>12429.032</v>
       </c>
       <c r="G89">
         <v>875.6</v>
@@ -8591,37 +8591,37 @@
         <v>851.8</v>
       </c>
       <c r="M89">
-        <v>2467.3888344</v>
+        <v>2495.7496256</v>
       </c>
       <c r="N89">
-        <v>-1615.5888344</v>
+        <v>-1643.9496256</v>
       </c>
       <c r="O89">
-        <v>-323.1177668800001</v>
+        <v>-328.78992512</v>
       </c>
       <c r="P89">
-        <v>-1292.47106752</v>
+        <v>-1315.15970048</v>
       </c>
       <c r="Q89">
-        <v>-1049.27106752</v>
+        <v>-1071.95970048</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3927150129432935</v>
+        <v>0.4216245973552347</v>
       </c>
       <c r="T89">
-        <v>6.762019314838819</v>
+        <v>7.325520924408722</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.06904465061398674</v>
+        <v>0.06826005231155508</v>
       </c>
       <c r="W89">
-        <v>0.1869358341567114</v>
+        <v>0.1870933814958397</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3452232530699337</v>
+        <v>0.3413002615577754</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2152371273989671</v>
+        <v>0.2167871273989671</v>
       </c>
       <c r="C90">
-        <v>-7804.302829158954</v>
+        <v>-7979.527722151031</v>
       </c>
       <c r="D90">
-        <v>3749.129170841045</v>
+        <v>3715.14327784897</v>
       </c>
       <c r="E90">
-        <v>12379.632</v>
+        <v>12520.871</v>
       </c>
       <c r="F90">
-        <v>12429.032</v>
+        <v>12570.271</v>
       </c>
       <c r="G90">
         <v>875.6</v>
@@ -8673,37 +8673,37 @@
         <v>851.8</v>
       </c>
       <c r="M90">
-        <v>2495.7496256</v>
+        <v>2524.1104168</v>
       </c>
       <c r="N90">
-        <v>-1643.9496256</v>
+        <v>-1672.3104168</v>
       </c>
       <c r="O90">
-        <v>-328.78992512</v>
+        <v>-334.4620833600001</v>
       </c>
       <c r="P90">
-        <v>-1315.15970048</v>
+        <v>-1337.84833344</v>
       </c>
       <c r="Q90">
-        <v>-1071.95970048</v>
+        <v>-1094.64833344</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4216245973552347</v>
+        <v>0.4557904698420742</v>
       </c>
       <c r="T90">
-        <v>7.325520924408722</v>
+        <v>7.991477372082243</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.06826005231155508</v>
+        <v>0.06749308543164996</v>
       </c>
       <c r="W90">
-        <v>0.1870933814958397</v>
+        <v>0.1872473884453247</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3413002615577754</v>
+        <v>0.3374654271582498</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2167871273989671</v>
+        <v>0.2183371273989672</v>
       </c>
       <c r="C91">
-        <v>-7979.527722151031</v>
+        <v>-8154.141985594187</v>
       </c>
       <c r="D91">
-        <v>3715.14327784897</v>
+        <v>3681.768014405814</v>
       </c>
       <c r="E91">
-        <v>12520.871</v>
+        <v>12662.11</v>
       </c>
       <c r="F91">
-        <v>12570.271</v>
+        <v>12711.51</v>
       </c>
       <c r="G91">
         <v>875.6</v>
@@ -8755,37 +8755,37 @@
         <v>851.8</v>
       </c>
       <c r="M91">
-        <v>2524.1104168</v>
+        <v>2552.471208</v>
       </c>
       <c r="N91">
-        <v>-1672.3104168</v>
+        <v>-1700.671208</v>
       </c>
       <c r="O91">
-        <v>-334.4620833600001</v>
+        <v>-340.1342416</v>
       </c>
       <c r="P91">
-        <v>-1337.84833344</v>
+        <v>-1360.5369664</v>
       </c>
       <c r="Q91">
-        <v>-1094.64833344</v>
+        <v>-1117.3369664</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4557904698420742</v>
+        <v>0.4967895168262817</v>
       </c>
       <c r="T91">
-        <v>7.991477372082243</v>
+        <v>8.790625109290469</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.06749308543164996</v>
+        <v>0.06674316226018719</v>
       </c>
       <c r="W91">
-        <v>0.1872473884453247</v>
+        <v>0.1873979730181544</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3374654271582498</v>
+        <v>0.333715811300936</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2183371273989672</v>
+        <v>0.2198871273989672</v>
       </c>
       <c r="C92">
-        <v>-8154.141985594187</v>
+        <v>-8328.161929869579</v>
       </c>
       <c r="D92">
-        <v>3681.768014405814</v>
+        <v>3648.987070130421</v>
       </c>
       <c r="E92">
-        <v>12662.11</v>
+        <v>12803.349</v>
       </c>
       <c r="F92">
-        <v>12711.51</v>
+        <v>12852.749</v>
       </c>
       <c r="G92">
         <v>875.6</v>
@@ -8837,37 +8837,37 @@
         <v>851.8</v>
       </c>
       <c r="M92">
-        <v>2552.471208</v>
+        <v>2580.8319992</v>
       </c>
       <c r="N92">
-        <v>-1700.671208</v>
+        <v>-1729.0319992</v>
       </c>
       <c r="O92">
-        <v>-340.1342416</v>
+        <v>-345.80639984</v>
       </c>
       <c r="P92">
-        <v>-1360.5369664</v>
+        <v>-1383.22559936</v>
       </c>
       <c r="Q92">
-        <v>-1117.3369664</v>
+        <v>-1140.02559936</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4967895168262817</v>
+        <v>0.5468994631403129</v>
       </c>
       <c r="T92">
-        <v>8.790625109290469</v>
+        <v>9.767361232544964</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.06674316226018719</v>
+        <v>0.06600972091666864</v>
       </c>
       <c r="W92">
-        <v>0.1873979730181544</v>
+        <v>0.1875452480399329</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.333715811300936</v>
+        <v>0.3300486045833432</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2198871273989672</v>
+        <v>0.2214371273989671</v>
       </c>
       <c r="C93">
-        <v>-8328.161929869579</v>
+        <v>-8501.60328960104</v>
       </c>
       <c r="D93">
-        <v>3648.987070130421</v>
+        <v>3616.784710398959</v>
       </c>
       <c r="E93">
-        <v>12803.349</v>
+        <v>12944.588</v>
       </c>
       <c r="F93">
-        <v>12852.749</v>
+        <v>12993.988</v>
       </c>
       <c r="G93">
         <v>875.6</v>
@@ -8919,37 +8919,37 @@
         <v>851.8</v>
       </c>
       <c r="M93">
-        <v>2580.8319992</v>
+        <v>2609.1927904</v>
       </c>
       <c r="N93">
-        <v>-1729.0319992</v>
+        <v>-1757.3927904</v>
       </c>
       <c r="O93">
-        <v>-345.80639984</v>
+        <v>-351.47855808</v>
       </c>
       <c r="P93">
-        <v>-1383.22559936</v>
+        <v>-1405.91423232</v>
       </c>
       <c r="Q93">
-        <v>-1140.02559936</v>
+        <v>-1162.71423232</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5468994631403129</v>
+        <v>0.6095368960328522</v>
       </c>
       <c r="T93">
-        <v>9.767361232544964</v>
+        <v>10.98828138661309</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.06600972091666864</v>
+        <v>0.06529222395018312</v>
       </c>
       <c r="W93">
-        <v>0.1875452480399329</v>
+        <v>0.1876893214308032</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3300486045833432</v>
+        <v>0.3264611197509156</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2214371273989671</v>
+        <v>0.2229871273989671</v>
       </c>
       <c r="C94">
-        <v>-8501.60328960104</v>
+        <v>-8674.481248838161</v>
       </c>
       <c r="D94">
-        <v>3616.784710398959</v>
+        <v>3585.145751161839</v>
       </c>
       <c r="E94">
-        <v>12944.588</v>
+        <v>13085.827</v>
       </c>
       <c r="F94">
-        <v>12993.988</v>
+        <v>13135.227</v>
       </c>
       <c r="G94">
         <v>875.6</v>
@@ -9001,37 +9001,37 @@
         <v>851.8</v>
       </c>
       <c r="M94">
-        <v>2609.1927904</v>
+        <v>2637.5535816</v>
       </c>
       <c r="N94">
-        <v>-1757.3927904</v>
+        <v>-1785.7535816</v>
       </c>
       <c r="O94">
-        <v>-351.47855808</v>
+        <v>-357.1507163200001</v>
       </c>
       <c r="P94">
-        <v>-1405.91423232</v>
+        <v>-1428.60286528</v>
       </c>
       <c r="Q94">
-        <v>-1162.71423232</v>
+        <v>-1185.40286528</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6095368960328522</v>
+        <v>0.6900707383232598</v>
       </c>
       <c r="T94">
-        <v>10.98828138661309</v>
+        <v>12.55803587041496</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.06529222395018312</v>
+        <v>0.0645901570259876</v>
       </c>
       <c r="W94">
-        <v>0.1876893214308032</v>
+        <v>0.1878302964691817</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3264611197509156</v>
+        <v>0.322950785129938</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2229871273989671</v>
+        <v>0.2245371273989671</v>
       </c>
       <c r="C95">
-        <v>-8674.481248838161</v>
+        <v>-8846.810464929064</v>
       </c>
       <c r="D95">
-        <v>3585.145751161839</v>
+        <v>3554.055535070937</v>
       </c>
       <c r="E95">
-        <v>13085.827</v>
+        <v>13227.066</v>
       </c>
       <c r="F95">
-        <v>13135.227</v>
+        <v>13276.466</v>
       </c>
       <c r="G95">
         <v>875.6</v>
@@ -9083,37 +9083,37 @@
         <v>851.8</v>
       </c>
       <c r="M95">
-        <v>2637.5535816</v>
+        <v>2665.9143728</v>
       </c>
       <c r="N95">
-        <v>-1785.7535816</v>
+        <v>-1814.1143728</v>
       </c>
       <c r="O95">
-        <v>-357.1507163200001</v>
+        <v>-362.8228745600001</v>
       </c>
       <c r="P95">
-        <v>-1428.60286528</v>
+        <v>-1451.29149824</v>
       </c>
       <c r="Q95">
-        <v>-1185.40286528</v>
+        <v>-1208.09149824</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6900707383232598</v>
+        <v>0.79744919471047</v>
       </c>
       <c r="T95">
-        <v>12.55803587041496</v>
+        <v>14.65104184881746</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.0645901570259876</v>
+        <v>0.06390302769592389</v>
       </c>
       <c r="W95">
-        <v>0.1878302964691817</v>
+        <v>0.1879682720386585</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.322950785129938</v>
+        <v>0.3195151384796194</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2245371273989671</v>
+        <v>0.2260871273989672</v>
       </c>
       <c r="C96">
-        <v>-8846.810464929064</v>
+        <v>-9018.605091161709</v>
       </c>
       <c r="D96">
-        <v>3554.055535070937</v>
+        <v>3523.49990883829</v>
       </c>
       <c r="E96">
-        <v>13227.066</v>
+        <v>13368.305</v>
       </c>
       <c r="F96">
-        <v>13276.466</v>
+        <v>13417.705</v>
       </c>
       <c r="G96">
         <v>875.6</v>
@@ -9165,37 +9165,37 @@
         <v>851.8</v>
       </c>
       <c r="M96">
-        <v>2665.9143728</v>
+        <v>2694.275164</v>
       </c>
       <c r="N96">
-        <v>-1814.1143728</v>
+        <v>-1842.475164</v>
       </c>
       <c r="O96">
-        <v>-362.8228745600001</v>
+        <v>-368.4950328</v>
       </c>
       <c r="P96">
-        <v>-1451.29149824</v>
+        <v>-1473.9801312</v>
       </c>
       <c r="Q96">
-        <v>-1208.09149824</v>
+        <v>-1230.7801312</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.79744919471047</v>
+        <v>0.9477790336525644</v>
       </c>
       <c r="T96">
-        <v>14.65104184881746</v>
+        <v>17.58125021858096</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.06390302769592389</v>
+        <v>0.06323036424649313</v>
       </c>
       <c r="W96">
-        <v>0.1879682720386585</v>
+        <v>0.1881033428593042</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3195151384796194</v>
+        <v>0.3161518212324655</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2260871273989672</v>
+        <v>0.2276371273989671</v>
       </c>
       <c r="C97">
-        <v>-9018.605091161709</v>
+        <v>-9189.878798247222</v>
       </c>
       <c r="D97">
-        <v>3523.49990883829</v>
+        <v>3493.465201752779</v>
       </c>
       <c r="E97">
-        <v>13368.305</v>
+        <v>13509.544</v>
       </c>
       <c r="F97">
-        <v>13417.705</v>
+        <v>13558.944</v>
       </c>
       <c r="G97">
         <v>875.6</v>
@@ -9247,37 +9247,37 @@
         <v>851.8</v>
       </c>
       <c r="M97">
-        <v>2694.275164</v>
+        <v>2722.6359552</v>
       </c>
       <c r="N97">
-        <v>-1842.475164</v>
+        <v>-1870.8359552</v>
       </c>
       <c r="O97">
-        <v>-368.4950328</v>
+        <v>-374.1671910400001</v>
       </c>
       <c r="P97">
-        <v>-1473.9801312</v>
+        <v>-1496.66876416</v>
       </c>
       <c r="Q97">
-        <v>-1230.7801312</v>
+        <v>-1253.46876416</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9477790336525644</v>
+        <v>1.173273792065706</v>
       </c>
       <c r="T97">
-        <v>17.58125021858096</v>
+        <v>21.97656277322621</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.06323036424649313</v>
+        <v>0.06257171461892548</v>
       </c>
       <c r="W97">
-        <v>0.1881033428593042</v>
+        <v>0.1882355997045198</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3161518212324655</v>
+        <v>0.3128585730946274</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2276371273989671</v>
+        <v>0.2291871273989671</v>
       </c>
       <c r="C98">
-        <v>-9189.87879824722</v>
+        <v>-9360.644794713753</v>
       </c>
       <c r="D98">
-        <v>3493.465201752779</v>
+        <v>3463.938205286247</v>
       </c>
       <c r="E98">
-        <v>13509.544</v>
+        <v>13650.783</v>
       </c>
       <c r="F98">
-        <v>13558.944</v>
+        <v>13700.183</v>
       </c>
       <c r="G98">
         <v>875.6</v>
@@ -9329,37 +9329,37 @@
         <v>851.8</v>
       </c>
       <c r="M98">
-        <v>2722.6359552</v>
+        <v>2750.9967464</v>
       </c>
       <c r="N98">
-        <v>-1870.8359552</v>
+        <v>-1899.1967464</v>
       </c>
       <c r="O98">
-        <v>-374.16719104</v>
+        <v>-379.8393492800001</v>
       </c>
       <c r="P98">
-        <v>-1496.66876416</v>
+        <v>-1519.35739712</v>
       </c>
       <c r="Q98">
-        <v>-1253.46876416</v>
+        <v>-1276.15739712</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.173273792065703</v>
+        <v>1.549098389420938</v>
       </c>
       <c r="T98">
-        <v>21.97656277322615</v>
+        <v>29.30208369763487</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.06257171461892549</v>
+        <v>0.06192664539604997</v>
       </c>
       <c r="W98">
-        <v>0.1882355997045198</v>
+        <v>0.1883651296044732</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3128585730946274</v>
+        <v>0.3096332269802498</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2291871273989671</v>
+        <v>0.2307371273989671</v>
       </c>
       <c r="C99">
-        <v>-9360.644794713753</v>
+        <v>-9530.915846274773</v>
       </c>
       <c r="D99">
-        <v>3463.938205286247</v>
+        <v>3434.906153725225</v>
       </c>
       <c r="E99">
-        <v>13650.783</v>
+        <v>13792.022</v>
       </c>
       <c r="F99">
-        <v>13700.183</v>
+        <v>13841.422</v>
       </c>
       <c r="G99">
         <v>875.6</v>
@@ -9411,37 +9411,37 @@
         <v>851.8</v>
       </c>
       <c r="M99">
-        <v>2750.9967464</v>
+        <v>2779.3575376</v>
       </c>
       <c r="N99">
-        <v>-1899.1967464</v>
+        <v>-1927.5575376</v>
       </c>
       <c r="O99">
-        <v>-379.8393492800001</v>
+        <v>-385.51150752</v>
       </c>
       <c r="P99">
-        <v>-1519.35739712</v>
+        <v>-1542.04603008</v>
       </c>
       <c r="Q99">
-        <v>-1276.15739712</v>
+        <v>-1298.84603008</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.549098389420938</v>
+        <v>2.300747584131406</v>
       </c>
       <c r="T99">
-        <v>29.30208369763487</v>
+        <v>43.95312554645229</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.06192664539604997</v>
+        <v>0.06129474085119231</v>
       </c>
       <c r="W99">
-        <v>0.1883651296044732</v>
+        <v>0.1884920160370806</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3096332269802498</v>
+        <v>0.3064737042559615</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2307371273989671</v>
+        <v>0.2322871273989671</v>
       </c>
       <c r="C100">
-        <v>-9530.915846274773</v>
+        <v>-9700.704294231487</v>
       </c>
       <c r="D100">
-        <v>3434.906153725225</v>
+        <v>3406.356705768513</v>
       </c>
       <c r="E100">
-        <v>13792.022</v>
+        <v>13933.261</v>
       </c>
       <c r="F100">
-        <v>13841.422</v>
+        <v>13982.661</v>
       </c>
       <c r="G100">
         <v>875.6</v>
@@ -9493,37 +9493,37 @@
         <v>851.8</v>
       </c>
       <c r="M100">
-        <v>2779.3575376</v>
+        <v>2807.7183288</v>
       </c>
       <c r="N100">
-        <v>-1927.5575376</v>
+        <v>-1955.9183288</v>
       </c>
       <c r="O100">
-        <v>-385.51150752</v>
+        <v>-391.1836657600001</v>
       </c>
       <c r="P100">
-        <v>-1542.04603008</v>
+        <v>-1564.73466304</v>
       </c>
       <c r="Q100">
-        <v>-1298.84603008</v>
+        <v>-1321.53466304</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.300747584131406</v>
+        <v>4.555695168262812</v>
       </c>
       <c r="T100">
-        <v>43.95312554645229</v>
+        <v>87.90625109290458</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.06129474085119231</v>
+        <v>0.06067560205471562</v>
       </c>
       <c r="W100">
-        <v>0.1884920160370806</v>
+        <v>0.1886163391074131</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3064737042559615</v>
+        <v>0.3033780102735781</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2322871273989671</v>
-      </c>
-      <c r="C101">
-        <v>-9700.704294231487</v>
-      </c>
-      <c r="D101">
-        <v>3406.356705768513</v>
-      </c>
-      <c r="E101">
-        <v>13933.261</v>
-      </c>
-      <c r="F101">
-        <v>13982.661</v>
-      </c>
-      <c r="G101">
-        <v>875.6</v>
-      </c>
-      <c r="H101">
-        <v>14074.5</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1095</v>
-      </c>
-      <c r="K101">
-        <v>243.2</v>
-      </c>
-      <c r="L101">
-        <v>851.8</v>
-      </c>
-      <c r="M101">
-        <v>2807.7183288</v>
-      </c>
-      <c r="N101">
-        <v>-1955.9183288</v>
-      </c>
-      <c r="O101">
-        <v>-391.1836657600001</v>
-      </c>
-      <c r="P101">
-        <v>-1564.73466304</v>
-      </c>
-      <c r="Q101">
-        <v>-1321.53466304</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.555695168262812</v>
-      </c>
-      <c r="T101">
-        <v>87.90625109290458</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.06067560205471562</v>
-      </c>
-      <c r="W101">
-        <v>0.1886163391074131</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3033780102735781</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
